--- a/calc/kema-invest-3520-0-Ferizaj-ekzekutimi.xlsx
+++ b/calc/kema-invest-3520-0-Ferizaj-ekzekutimi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ferizaj\Ferizaj\Ingjinierike\Macropus\calc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valon\OneDrive\Desktop\puna\Ferizaj\kema-invest-3520-0-Ferizaj\calc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7422AA-DC02-45BA-98B6-D4FAD9A8F7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1DA0AE-563C-478A-B047-A9857FDDD323}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="240" windowWidth="27435" windowHeight="15960" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="240" windowWidth="27432" windowHeight="15960" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$657</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1340,9 +1340,8 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1372,6 +1371,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1442,6 +1444,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1449,6 +1454,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1460,17 +1471,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1508,7 +1508,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F399456-FFFA-4806-B53B-2B24D3A1E278}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1564,7 +1564,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F6037-E9CB-49EA-8E58-E0677C590B64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1625,7 +1625,7 @@
         <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07937452-2E79-4669-8F05-2069DFF859A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1697,7 +1697,7 @@
         <xdr:cNvPr id="6" name="TextBox 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD9F1684-A2E1-4EF0-89C9-1E368E9A0FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1772,7 +1772,7 @@
         <xdr:cNvPr id="7" name="TextBox 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D2CC83-FE69-4C93-84EB-099D36DB81C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1838,7 +1838,7 @@
         <xdr:cNvPr id="8" name="Picture 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F399456-FFFA-4806-B53B-2B24D3A1E278}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1894,7 +1894,7 @@
         <xdr:cNvPr id="9" name="TextBox 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F6037-E9CB-49EA-8E58-E0677C590B64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1955,7 +1955,7 @@
         <xdr:cNvPr id="10" name="TextBox 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07937452-2E79-4669-8F05-2069DFF859A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2016,7 +2016,7 @@
         <xdr:cNvPr id="11" name="TextBox 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD9F1684-A2E1-4EF0-89C9-1E368E9A0FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2091,7 +2091,7 @@
         <xdr:cNvPr id="12" name="TextBox 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D2CC83-FE69-4C93-84EB-099D36DB81C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2157,7 +2157,7 @@
         <xdr:cNvPr id="13" name="Picture 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F399456-FFFA-4806-B53B-2B24D3A1E278}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2213,7 +2213,7 @@
         <xdr:cNvPr id="14" name="TextBox 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F6037-E9CB-49EA-8E58-E0677C590B64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2274,7 +2274,7 @@
         <xdr:cNvPr id="15" name="TextBox 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07937452-2E79-4669-8F05-2069DFF859A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2335,7 +2335,7 @@
         <xdr:cNvPr id="16" name="TextBox 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD9F1684-A2E1-4EF0-89C9-1E368E9A0FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2410,7 +2410,7 @@
         <xdr:cNvPr id="17" name="TextBox 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D2CC83-FE69-4C93-84EB-099D36DB81C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2476,7 +2476,7 @@
         <xdr:cNvPr id="18" name="Picture 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F399456-FFFA-4806-B53B-2B24D3A1E278}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2532,7 +2532,7 @@
         <xdr:cNvPr id="19" name="TextBox 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F6037-E9CB-49EA-8E58-E0677C590B64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2593,7 +2593,7 @@
         <xdr:cNvPr id="20" name="TextBox 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07937452-2E79-4669-8F05-2069DFF859A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2654,7 +2654,7 @@
         <xdr:cNvPr id="21" name="TextBox 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD9F1684-A2E1-4EF0-89C9-1E368E9A0FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2729,7 +2729,7 @@
         <xdr:cNvPr id="22" name="TextBox 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D2CC83-FE69-4C93-84EB-099D36DB81C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2795,7 +2795,7 @@
         <xdr:cNvPr id="23" name="Picture 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F399456-FFFA-4806-B53B-2B24D3A1E278}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2851,7 +2851,7 @@
         <xdr:cNvPr id="24" name="TextBox 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F6037-E9CB-49EA-8E58-E0677C590B64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2912,7 +2912,7 @@
         <xdr:cNvPr id="25" name="TextBox 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07937452-2E79-4669-8F05-2069DFF859A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2973,7 +2973,7 @@
         <xdr:cNvPr id="26" name="TextBox 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD9F1684-A2E1-4EF0-89C9-1E368E9A0FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3048,7 +3048,7 @@
         <xdr:cNvPr id="27" name="TextBox 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D2CC83-FE69-4C93-84EB-099D36DB81C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3114,7 +3114,7 @@
         <xdr:cNvPr id="28" name="Picture 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F399456-FFFA-4806-B53B-2B24D3A1E278}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3170,7 +3170,7 @@
         <xdr:cNvPr id="29" name="TextBox 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F6037-E9CB-49EA-8E58-E0677C590B64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3231,7 +3231,7 @@
         <xdr:cNvPr id="30" name="TextBox 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07937452-2E79-4669-8F05-2069DFF859A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3292,7 +3292,7 @@
         <xdr:cNvPr id="31" name="TextBox 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD9F1684-A2E1-4EF0-89C9-1E368E9A0FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3367,7 +3367,7 @@
         <xdr:cNvPr id="32" name="TextBox 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D2CC83-FE69-4C93-84EB-099D36DB81C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3433,7 +3433,7 @@
         <xdr:cNvPr id="33" name="Picture 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F399456-FFFA-4806-B53B-2B24D3A1E278}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3489,7 +3489,7 @@
         <xdr:cNvPr id="34" name="TextBox 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F6037-E9CB-49EA-8E58-E0677C590B64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3550,7 +3550,7 @@
         <xdr:cNvPr id="35" name="TextBox 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07937452-2E79-4669-8F05-2069DFF859A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3611,7 +3611,7 @@
         <xdr:cNvPr id="36" name="TextBox 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD9F1684-A2E1-4EF0-89C9-1E368E9A0FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3686,7 +3686,7 @@
         <xdr:cNvPr id="37" name="TextBox 36">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D2CC83-FE69-4C93-84EB-099D36DB81C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3752,7 +3752,7 @@
         <xdr:cNvPr id="38" name="Picture 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F399456-FFFA-4806-B53B-2B24D3A1E278}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3808,7 +3808,7 @@
         <xdr:cNvPr id="39" name="TextBox 38">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F6037-E9CB-49EA-8E58-E0677C590B64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3869,7 +3869,7 @@
         <xdr:cNvPr id="40" name="TextBox 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07937452-2E79-4669-8F05-2069DFF859A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3930,7 +3930,7 @@
         <xdr:cNvPr id="41" name="TextBox 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD9F1684-A2E1-4EF0-89C9-1E368E9A0FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4005,7 +4005,7 @@
         <xdr:cNvPr id="42" name="TextBox 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D2CC83-FE69-4C93-84EB-099D36DB81C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4071,7 +4071,7 @@
         <xdr:cNvPr id="43" name="Picture 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F399456-FFFA-4806-B53B-2B24D3A1E278}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4127,7 +4127,7 @@
         <xdr:cNvPr id="44" name="TextBox 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F6037-E9CB-49EA-8E58-E0677C590B64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4188,7 +4188,7 @@
         <xdr:cNvPr id="45" name="TextBox 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07937452-2E79-4669-8F05-2069DFF859A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4249,7 +4249,7 @@
         <xdr:cNvPr id="46" name="TextBox 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD9F1684-A2E1-4EF0-89C9-1E368E9A0FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4324,7 +4324,7 @@
         <xdr:cNvPr id="47" name="TextBox 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D2CC83-FE69-4C93-84EB-099D36DB81C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4418,7 +4418,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -4470,7 +4470,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -4673,128 +4673,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V657"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53"/>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-    </row>
-    <row r="2" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-    </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="65"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+    </row>
+    <row r="2" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+    </row>
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-    </row>
-    <row r="4" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-    </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="54"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C8" s="55"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="57"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C9" s="58"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="60"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="61"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="63"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+    </row>
+    <row r="4" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="55"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="55"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+    </row>
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="55"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C8" s="56"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C9" s="59"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="61"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C10" s="62"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="64"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C13" s="4" t="s">
         <v>0</v>
       </c>
@@ -4817,7 +4817,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C14" s="7">
         <v>1139</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C15" s="7">
         <v>1140</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C16" s="7">
         <v>3000</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C17" s="7">
         <v>1114</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C18" s="11">
         <v>1115</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C19" s="11">
         <v>1116</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C20" s="11">
         <v>1117</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C21" s="11">
         <v>1118</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C22" s="11">
         <v>1119</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C23" s="11">
         <v>1120</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C24" s="11">
         <v>1121</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C25" s="11">
         <v>1122</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C26" s="11">
         <v>1113</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C27" s="11">
         <v>3018</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C28" s="11">
         <v>3019</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C29" s="11">
         <v>3020</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C30" s="11">
         <v>3021</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C31" s="11">
         <v>3022</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C32" s="11">
         <v>3016</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C33" s="15">
         <v>3033</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C34" s="19"/>
       <c r="D34" s="20"/>
       <c r="E34" s="20"/>
@@ -5286,7 +5286,7 @@
       <c r="H34" s="19"/>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="3:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C35" s="4" t="s">
         <v>0</v>
       </c>
@@ -5309,7 +5309,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C36" s="7">
         <v>3036</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C37" s="7">
         <v>3038</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C38" s="7">
         <v>3040</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C39" s="7">
         <v>3042</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C40" s="11">
         <v>3044</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C41" s="11">
         <v>3046</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C42" s="11">
         <v>3048</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C43" s="11">
         <v>3050</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C44" s="11">
         <v>3052</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C45" s="11">
         <v>3054</v>
       </c>
@@ -5539,7 +5539,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C46" s="11">
         <v>3056</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C47" s="11">
         <v>3058</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C48" s="11">
         <v>3060</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C49" s="11">
         <v>3062</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C50" s="11">
         <v>3064</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C51" s="11">
         <v>3065</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C52" s="11">
         <v>3066</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C53" s="11">
         <v>3067</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C54" s="11">
         <v>3068</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C55" s="11">
         <v>3069</v>
       </c>
@@ -5769,7 +5769,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C56" s="11">
         <v>3070</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="2:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C57" s="11">
         <v>3071</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C58" s="15">
         <v>3034</v>
       </c>
@@ -5838,180 +5838,180 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B62" s="81" t="s">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B62" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="81"/>
-      <c r="D62" s="81"/>
-      <c r="E62" s="81"/>
-      <c r="F62" s="81"/>
-      <c r="G62" s="81"/>
-      <c r="H62" s="81"/>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B63" s="81"/>
-      <c r="C63" s="81"/>
-      <c r="D63" s="81"/>
-      <c r="E63" s="81"/>
-      <c r="F63" s="81"/>
-      <c r="G63" s="81"/>
-      <c r="H63" s="81"/>
-    </row>
-    <row r="69" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C62" s="83"/>
+      <c r="D62" s="83"/>
+      <c r="E62" s="83"/>
+      <c r="F62" s="83"/>
+      <c r="G62" s="83"/>
+      <c r="H62" s="83"/>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B63" s="83"/>
+      <c r="C63" s="83"/>
+      <c r="D63" s="83"/>
+      <c r="E63" s="83"/>
+      <c r="F63" s="83"/>
+      <c r="G63" s="83"/>
+      <c r="H63" s="83"/>
+    </row>
+    <row r="69" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I69" s="3"/>
     </row>
-    <row r="70" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="64" t="s">
+      <c r="E70" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F70" s="65"/>
-      <c r="G70" s="66"/>
-      <c r="H70" s="67" t="s">
+      <c r="F70" s="67"/>
+      <c r="G70" s="68"/>
+      <c r="H70" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I70" s="68"/>
-      <c r="J70" s="71"/>
-      <c r="K70" s="72"/>
-    </row>
-    <row r="71" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="75" t="s">
+      <c r="I70" s="70"/>
+      <c r="J70" s="73"/>
+      <c r="K70" s="74"/>
+    </row>
+    <row r="71" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B71" s="76"/>
-      <c r="C71" s="76"/>
-      <c r="D71" s="77"/>
-      <c r="E71" s="78">
+      <c r="B71" s="78"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="79"/>
+      <c r="E71" s="80">
         <v>140</v>
       </c>
-      <c r="F71" s="79"/>
-      <c r="G71" s="80"/>
-      <c r="H71" s="69"/>
-      <c r="I71" s="70"/>
-      <c r="J71" s="73"/>
-      <c r="K71" s="74"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="53"/>
-      <c r="B72" s="53"/>
-      <c r="C72" s="53"/>
-      <c r="D72" s="53"/>
-      <c r="E72" s="53"/>
-      <c r="F72" s="53"/>
-      <c r="G72" s="53"/>
-      <c r="H72" s="53"/>
-      <c r="I72" s="53"/>
-      <c r="J72" s="53"/>
-      <c r="K72" s="53"/>
-    </row>
-    <row r="73" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="53"/>
-      <c r="B73" s="53"/>
-      <c r="C73" s="53"/>
-      <c r="D73" s="53"/>
-      <c r="E73" s="53"/>
-      <c r="F73" s="53"/>
-      <c r="G73" s="53"/>
-      <c r="H73" s="53"/>
-      <c r="I73" s="53"/>
-      <c r="J73" s="53"/>
-      <c r="K73" s="53"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="54" t="s">
+      <c r="F71" s="81"/>
+      <c r="G71" s="82"/>
+      <c r="H71" s="71"/>
+      <c r="I71" s="72"/>
+      <c r="J71" s="75"/>
+      <c r="K71" s="76"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="65"/>
+      <c r="B72" s="65"/>
+      <c r="C72" s="65"/>
+      <c r="D72" s="65"/>
+      <c r="E72" s="65"/>
+      <c r="F72" s="65"/>
+      <c r="G72" s="65"/>
+      <c r="H72" s="65"/>
+      <c r="I72" s="65"/>
+      <c r="J72" s="65"/>
+      <c r="K72" s="65"/>
+    </row>
+    <row r="73" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="65"/>
+      <c r="B73" s="65"/>
+      <c r="C73" s="65"/>
+      <c r="D73" s="65"/>
+      <c r="E73" s="65"/>
+      <c r="F73" s="65"/>
+      <c r="G73" s="65"/>
+      <c r="H73" s="65"/>
+      <c r="I73" s="65"/>
+      <c r="J73" s="65"/>
+      <c r="K73" s="65"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B74" s="54"/>
-      <c r="C74" s="54"/>
-      <c r="D74" s="54"/>
-      <c r="E74" s="54"/>
-      <c r="F74" s="54"/>
-      <c r="G74" s="54"/>
-      <c r="H74" s="54"/>
-      <c r="I74" s="54"/>
-      <c r="J74" s="54"/>
-      <c r="K74" s="54"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="54"/>
-      <c r="B75" s="54"/>
-      <c r="C75" s="54"/>
-      <c r="D75" s="54"/>
-      <c r="E75" s="54"/>
-      <c r="F75" s="54"/>
-      <c r="G75" s="54"/>
-      <c r="H75" s="54"/>
-      <c r="I75" s="54"/>
-      <c r="J75" s="54"/>
-      <c r="K75" s="54"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="54"/>
-      <c r="B76" s="54"/>
-      <c r="C76" s="54"/>
-      <c r="D76" s="54"/>
-      <c r="E76" s="54"/>
-      <c r="F76" s="54"/>
-      <c r="G76" s="54"/>
-      <c r="H76" s="54"/>
-      <c r="I76" s="54"/>
-      <c r="J76" s="54"/>
-      <c r="K76" s="54"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="54"/>
-      <c r="B77" s="54"/>
-      <c r="C77" s="54"/>
-      <c r="D77" s="54"/>
-      <c r="E77" s="54"/>
-      <c r="F77" s="54"/>
-      <c r="G77" s="54"/>
-      <c r="H77" s="54"/>
-      <c r="I77" s="54"/>
-      <c r="J77" s="54"/>
-      <c r="K77" s="54"/>
-    </row>
-    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C79" s="55"/>
-      <c r="D79" s="56"/>
-      <c r="E79" s="56"/>
-      <c r="F79" s="56"/>
-      <c r="G79" s="56"/>
-      <c r="H79" s="56"/>
-      <c r="I79" s="57"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C80" s="58"/>
-      <c r="D80" s="59"/>
-      <c r="E80" s="59"/>
-      <c r="F80" s="59"/>
-      <c r="G80" s="59"/>
-      <c r="H80" s="59"/>
-      <c r="I80" s="60"/>
-    </row>
-    <row r="81" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="61"/>
-      <c r="D81" s="62"/>
-      <c r="E81" s="62"/>
-      <c r="F81" s="62"/>
-      <c r="G81" s="62"/>
-      <c r="H81" s="62"/>
-      <c r="I81" s="63"/>
-    </row>
-    <row r="82" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B74" s="55"/>
+      <c r="C74" s="55"/>
+      <c r="D74" s="55"/>
+      <c r="E74" s="55"/>
+      <c r="F74" s="55"/>
+      <c r="G74" s="55"/>
+      <c r="H74" s="55"/>
+      <c r="I74" s="55"/>
+      <c r="J74" s="55"/>
+      <c r="K74" s="55"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="55"/>
+      <c r="B75" s="55"/>
+      <c r="C75" s="55"/>
+      <c r="D75" s="55"/>
+      <c r="E75" s="55"/>
+      <c r="F75" s="55"/>
+      <c r="G75" s="55"/>
+      <c r="H75" s="55"/>
+      <c r="I75" s="55"/>
+      <c r="J75" s="55"/>
+      <c r="K75" s="55"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="55"/>
+      <c r="B76" s="55"/>
+      <c r="C76" s="55"/>
+      <c r="D76" s="55"/>
+      <c r="E76" s="55"/>
+      <c r="F76" s="55"/>
+      <c r="G76" s="55"/>
+      <c r="H76" s="55"/>
+      <c r="I76" s="55"/>
+      <c r="J76" s="55"/>
+      <c r="K76" s="55"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="55"/>
+      <c r="B77" s="55"/>
+      <c r="C77" s="55"/>
+      <c r="D77" s="55"/>
+      <c r="E77" s="55"/>
+      <c r="F77" s="55"/>
+      <c r="G77" s="55"/>
+      <c r="H77" s="55"/>
+      <c r="I77" s="55"/>
+      <c r="J77" s="55"/>
+      <c r="K77" s="55"/>
+    </row>
+    <row r="78" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C79" s="56"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="58"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C80" s="59"/>
+      <c r="D80" s="60"/>
+      <c r="E80" s="60"/>
+      <c r="F80" s="60"/>
+      <c r="G80" s="60"/>
+      <c r="H80" s="60"/>
+      <c r="I80" s="61"/>
+    </row>
+    <row r="81" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C81" s="62"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="63"/>
+      <c r="I81" s="64"/>
+    </row>
+    <row r="82" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I82" s="3"/>
     </row>
-    <row r="83" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I83" s="3"/>
     </row>
-    <row r="84" spans="3:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C84" s="4" t="s">
         <v>0</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C85" s="7">
         <v>1000</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C86" s="7">
         <v>1001</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C87" s="7">
         <v>1002</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C88" s="7">
         <v>1003</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C89" s="11">
         <v>1004</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C90" s="11">
         <v>1005</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C91" s="11">
         <v>1006</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C92" s="11">
         <v>1007</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C93" s="11">
         <v>1008</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C94" s="11">
         <v>1009</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C95" s="11">
         <v>1133</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C96" s="11">
         <v>1134</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C97" s="11">
         <v>1135</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C98" s="11">
         <v>1136</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C99" s="11">
         <v>1137</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C100" s="15">
         <v>1138</v>
       </c>
@@ -6402,10 +6402,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I101" s="3"/>
     </row>
-    <row r="102" spans="3:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C102" s="4" t="s">
         <v>0</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C103" s="7">
         <v>1168</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C104" s="7">
         <v>1169</v>
       </c>
@@ -6474,7 +6474,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C105" s="7">
         <v>1170</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C106" s="7">
         <v>1171</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C107" s="11">
         <v>1172</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C108" s="11">
         <v>1173</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C109" s="11">
         <v>1174</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C110" s="11">
         <v>1175</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C111" s="11">
         <v>1176</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C112" s="11">
         <v>1177</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C113" s="11">
         <v>2000</v>
       </c>
@@ -6681,7 +6681,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C114" s="11">
         <v>2001</v>
       </c>
@@ -6704,7 +6704,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C115" s="11">
         <v>2002</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C116" s="11">
         <v>2003</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C117" s="11">
         <v>2004</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C118" s="15">
         <v>2005</v>
       </c>
@@ -6796,224 +6796,224 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I119" s="3"/>
     </row>
-    <row r="120" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I120" s="3"/>
     </row>
-    <row r="121" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I121" s="3"/>
     </row>
-    <row r="122" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I122" s="3"/>
     </row>
-    <row r="123" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I123" s="3"/>
     </row>
-    <row r="124" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I124" s="3"/>
     </row>
-    <row r="125" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I125" s="3"/>
     </row>
-    <row r="126" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I126" s="3"/>
     </row>
-    <row r="127" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I127" s="3"/>
     </row>
-    <row r="128" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I128" s="3"/>
     </row>
-    <row r="129" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I129" s="3"/>
     </row>
-    <row r="130" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I130" s="3"/>
     </row>
-    <row r="131" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I131" s="3"/>
     </row>
-    <row r="132" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I132" s="3"/>
     </row>
-    <row r="133" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I133" s="3"/>
     </row>
-    <row r="134" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I134" s="3"/>
     </row>
-    <row r="135" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I135" s="3"/>
     </row>
-    <row r="136" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I136" s="3"/>
     </row>
-    <row r="137" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I137" s="3"/>
     </row>
-    <row r="138" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I138" s="3"/>
     </row>
-    <row r="139" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I139" s="3"/>
     </row>
-    <row r="140" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I140" s="3"/>
     </row>
-    <row r="141" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I141" s="3"/>
     </row>
-    <row r="142" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I142" s="3"/>
     </row>
-    <row r="143" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="64" t="s">
+      <c r="E143" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F143" s="65"/>
-      <c r="G143" s="66"/>
-      <c r="H143" s="67" t="s">
+      <c r="F143" s="67"/>
+      <c r="G143" s="68"/>
+      <c r="H143" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I143" s="68"/>
-      <c r="J143" s="71"/>
-      <c r="K143" s="72"/>
-    </row>
-    <row r="144" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="75" t="s">
+      <c r="I143" s="70"/>
+      <c r="J143" s="73"/>
+      <c r="K143" s="74"/>
+    </row>
+    <row r="144" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B144" s="76"/>
-      <c r="C144" s="76"/>
-      <c r="D144" s="77"/>
-      <c r="E144" s="78">
+      <c r="B144" s="78"/>
+      <c r="C144" s="78"/>
+      <c r="D144" s="79"/>
+      <c r="E144" s="80">
         <v>140</v>
       </c>
-      <c r="F144" s="79"/>
-      <c r="G144" s="80"/>
-      <c r="H144" s="69"/>
-      <c r="I144" s="70"/>
-      <c r="J144" s="73"/>
-      <c r="K144" s="74"/>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145" s="53"/>
-      <c r="B145" s="53"/>
-      <c r="C145" s="53"/>
-      <c r="D145" s="53"/>
-      <c r="E145" s="53"/>
-      <c r="F145" s="53"/>
-      <c r="G145" s="53"/>
-      <c r="H145" s="53"/>
-      <c r="I145" s="53"/>
-      <c r="J145" s="53"/>
-      <c r="K145" s="53"/>
-    </row>
-    <row r="146" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="53"/>
-      <c r="B146" s="53"/>
-      <c r="C146" s="53"/>
-      <c r="D146" s="53"/>
-      <c r="E146" s="53"/>
-      <c r="F146" s="53"/>
-      <c r="G146" s="53"/>
-      <c r="H146" s="53"/>
-      <c r="I146" s="53"/>
-      <c r="J146" s="53"/>
-      <c r="K146" s="53"/>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" s="54" t="s">
+      <c r="F144" s="81"/>
+      <c r="G144" s="82"/>
+      <c r="H144" s="71"/>
+      <c r="I144" s="72"/>
+      <c r="J144" s="75"/>
+      <c r="K144" s="76"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A145" s="65"/>
+      <c r="B145" s="65"/>
+      <c r="C145" s="65"/>
+      <c r="D145" s="65"/>
+      <c r="E145" s="65"/>
+      <c r="F145" s="65"/>
+      <c r="G145" s="65"/>
+      <c r="H145" s="65"/>
+      <c r="I145" s="65"/>
+      <c r="J145" s="65"/>
+      <c r="K145" s="65"/>
+    </row>
+    <row r="146" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="65"/>
+      <c r="B146" s="65"/>
+      <c r="C146" s="65"/>
+      <c r="D146" s="65"/>
+      <c r="E146" s="65"/>
+      <c r="F146" s="65"/>
+      <c r="G146" s="65"/>
+      <c r="H146" s="65"/>
+      <c r="I146" s="65"/>
+      <c r="J146" s="65"/>
+      <c r="K146" s="65"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A147" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B147" s="54"/>
-      <c r="C147" s="54"/>
-      <c r="D147" s="54"/>
-      <c r="E147" s="54"/>
-      <c r="F147" s="54"/>
-      <c r="G147" s="54"/>
-      <c r="H147" s="54"/>
-      <c r="I147" s="54"/>
-      <c r="J147" s="54"/>
-      <c r="K147" s="54"/>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" s="54"/>
-      <c r="B148" s="54"/>
-      <c r="C148" s="54"/>
-      <c r="D148" s="54"/>
-      <c r="E148" s="54"/>
-      <c r="F148" s="54"/>
-      <c r="G148" s="54"/>
-      <c r="H148" s="54"/>
-      <c r="I148" s="54"/>
-      <c r="J148" s="54"/>
-      <c r="K148" s="54"/>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149" s="54"/>
-      <c r="B149" s="54"/>
-      <c r="C149" s="54"/>
-      <c r="D149" s="54"/>
-      <c r="E149" s="54"/>
-      <c r="F149" s="54"/>
-      <c r="G149" s="54"/>
-      <c r="H149" s="54"/>
-      <c r="I149" s="54"/>
-      <c r="J149" s="54"/>
-      <c r="K149" s="54"/>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150" s="54"/>
-      <c r="B150" s="54"/>
-      <c r="C150" s="54"/>
-      <c r="D150" s="54"/>
-      <c r="E150" s="54"/>
-      <c r="F150" s="54"/>
-      <c r="G150" s="54"/>
-      <c r="H150" s="54"/>
-      <c r="I150" s="54"/>
-      <c r="J150" s="54"/>
-      <c r="K150" s="54"/>
-    </row>
-    <row r="151" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C152" s="55"/>
-      <c r="D152" s="56"/>
-      <c r="E152" s="56"/>
-      <c r="F152" s="56"/>
-      <c r="G152" s="56"/>
-      <c r="H152" s="56"/>
-      <c r="I152" s="57"/>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C153" s="58"/>
-      <c r="D153" s="59"/>
-      <c r="E153" s="59"/>
-      <c r="F153" s="59"/>
-      <c r="G153" s="59"/>
-      <c r="H153" s="59"/>
-      <c r="I153" s="60"/>
-    </row>
-    <row r="154" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="61"/>
-      <c r="D154" s="62"/>
-      <c r="E154" s="62"/>
-      <c r="F154" s="62"/>
-      <c r="G154" s="62"/>
-      <c r="H154" s="62"/>
-      <c r="I154" s="63"/>
-    </row>
-    <row r="155" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="156" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B147" s="55"/>
+      <c r="C147" s="55"/>
+      <c r="D147" s="55"/>
+      <c r="E147" s="55"/>
+      <c r="F147" s="55"/>
+      <c r="G147" s="55"/>
+      <c r="H147" s="55"/>
+      <c r="I147" s="55"/>
+      <c r="J147" s="55"/>
+      <c r="K147" s="55"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A148" s="55"/>
+      <c r="B148" s="55"/>
+      <c r="C148" s="55"/>
+      <c r="D148" s="55"/>
+      <c r="E148" s="55"/>
+      <c r="F148" s="55"/>
+      <c r="G148" s="55"/>
+      <c r="H148" s="55"/>
+      <c r="I148" s="55"/>
+      <c r="J148" s="55"/>
+      <c r="K148" s="55"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A149" s="55"/>
+      <c r="B149" s="55"/>
+      <c r="C149" s="55"/>
+      <c r="D149" s="55"/>
+      <c r="E149" s="55"/>
+      <c r="F149" s="55"/>
+      <c r="G149" s="55"/>
+      <c r="H149" s="55"/>
+      <c r="I149" s="55"/>
+      <c r="J149" s="55"/>
+      <c r="K149" s="55"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A150" s="55"/>
+      <c r="B150" s="55"/>
+      <c r="C150" s="55"/>
+      <c r="D150" s="55"/>
+      <c r="E150" s="55"/>
+      <c r="F150" s="55"/>
+      <c r="G150" s="55"/>
+      <c r="H150" s="55"/>
+      <c r="I150" s="55"/>
+      <c r="J150" s="55"/>
+      <c r="K150" s="55"/>
+    </row>
+    <row r="151" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C152" s="56"/>
+      <c r="D152" s="57"/>
+      <c r="E152" s="57"/>
+      <c r="F152" s="57"/>
+      <c r="G152" s="57"/>
+      <c r="H152" s="57"/>
+      <c r="I152" s="58"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C153" s="59"/>
+      <c r="D153" s="60"/>
+      <c r="E153" s="60"/>
+      <c r="F153" s="60"/>
+      <c r="G153" s="60"/>
+      <c r="H153" s="60"/>
+      <c r="I153" s="61"/>
+    </row>
+    <row r="154" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C154" s="62"/>
+      <c r="D154" s="63"/>
+      <c r="E154" s="63"/>
+      <c r="F154" s="63"/>
+      <c r="G154" s="63"/>
+      <c r="H154" s="63"/>
+      <c r="I154" s="64"/>
+    </row>
+    <row r="155" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="156" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C156" s="4" t="s">
         <v>0</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C157" s="7">
         <v>3036</v>
       </c>
@@ -7059,7 +7059,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C158" s="7">
         <v>3038</v>
       </c>
@@ -7082,7 +7082,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C159" s="7">
         <v>3040</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C160" s="7">
         <v>3042</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="161" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C161" s="11">
         <v>3044</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="162" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C162" s="11">
         <v>3046</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="163" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C163" s="11">
         <v>3048</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="164" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C164" s="11">
         <v>3050</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="165" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C165" s="11">
         <v>3052</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="166" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C166" s="11">
         <v>3054</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="167" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C167" s="11">
         <v>3056</v>
       </c>
@@ -7289,7 +7289,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="168" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C168" s="11">
         <v>3058</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C169" s="11">
         <v>3060</v>
       </c>
@@ -7335,7 +7335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="170" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C170" s="11">
         <v>3062</v>
       </c>
@@ -7358,7 +7358,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C171" s="11">
         <v>3064</v>
       </c>
@@ -7381,7 +7381,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="172" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C172" s="11">
         <v>3065</v>
       </c>
@@ -7404,7 +7404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C173" s="11">
         <v>3066</v>
       </c>
@@ -7427,7 +7427,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="174" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C174" s="11">
         <v>3067</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="175" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C175" s="11">
         <v>3068</v>
       </c>
@@ -7473,7 +7473,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="176" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C176" s="11">
         <v>3069</v>
       </c>
@@ -7496,7 +7496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="177" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C177" s="11">
         <v>3070</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="178" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="178" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C178" s="11">
         <v>3071</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="179" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C179" s="15">
         <v>3034</v>
       </c>
@@ -7565,10 +7565,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="180" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I180" s="3"/>
     </row>
-    <row r="181" spans="3:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C181" s="4" t="s">
         <v>0</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="182" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="182" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C182" s="7">
         <v>3072</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="183" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C183" s="7">
         <v>3073</v>
       </c>
@@ -7637,7 +7637,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C184" s="7">
         <v>3074</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C185" s="7">
         <v>3075</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="186" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="186" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C186" s="11">
         <v>3076</v>
       </c>
@@ -7706,7 +7706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="187" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="187" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C187" s="11">
         <v>3077</v>
       </c>
@@ -7729,7 +7729,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="188" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="188" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C188" s="11">
         <v>3078</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="189" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C189" s="11">
         <v>3079</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="190" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C190" s="11">
         <v>3080</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="191" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="191" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C191" s="11">
         <v>3081</v>
       </c>
@@ -7821,7 +7821,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="192" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="192" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C192" s="11">
         <v>3082</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C193" s="11">
         <v>3083</v>
       </c>
@@ -7867,7 +7867,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="194" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C194" s="11">
         <v>3084</v>
       </c>
@@ -7890,7 +7890,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C195" s="11">
         <v>3085</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C196" s="11">
         <v>3086</v>
       </c>
@@ -7936,7 +7936,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="197" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C197" s="11">
         <v>3087</v>
       </c>
@@ -7959,7 +7959,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C198" s="11">
         <v>3089</v>
       </c>
@@ -7982,7 +7982,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="199" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C199" s="11">
         <v>3090</v>
       </c>
@@ -8005,7 +8005,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C200" s="11">
         <v>3094</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="201" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C201" s="11">
         <v>3096</v>
       </c>
@@ -8051,7 +8051,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="202" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C202" s="11">
         <v>3097</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C203" s="11">
         <v>3098</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="204" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C204" s="11">
         <v>3099</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="205" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C205" s="11">
         <v>3100</v>
       </c>
@@ -8143,7 +8143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="206" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C206" s="11">
         <v>3091</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="207" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C207" s="15">
         <v>3093</v>
       </c>
@@ -8189,175 +8189,175 @@
         <v>13</v>
       </c>
     </row>
-    <row r="208" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I208" s="3"/>
     </row>
-    <row r="209" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I209" s="3"/>
     </row>
-    <row r="210" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I210" s="3"/>
     </row>
-    <row r="211" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I211" s="3"/>
     </row>
-    <row r="212" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I212" s="3"/>
     </row>
-    <row r="213" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I213" s="3"/>
     </row>
-    <row r="214" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I214" s="3"/>
     </row>
-    <row r="215" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
-      <c r="E215" s="64" t="s">
+      <c r="E215" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F215" s="65"/>
-      <c r="G215" s="66"/>
-      <c r="H215" s="67" t="s">
+      <c r="F215" s="67"/>
+      <c r="G215" s="68"/>
+      <c r="H215" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I215" s="68"/>
-      <c r="J215" s="71"/>
-      <c r="K215" s="72"/>
-    </row>
-    <row r="216" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A216" s="75" t="s">
+      <c r="I215" s="70"/>
+      <c r="J215" s="73"/>
+      <c r="K215" s="74"/>
+    </row>
+    <row r="216" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A216" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B216" s="76"/>
-      <c r="C216" s="76"/>
-      <c r="D216" s="77"/>
-      <c r="E216" s="78">
+      <c r="B216" s="78"/>
+      <c r="C216" s="78"/>
+      <c r="D216" s="79"/>
+      <c r="E216" s="80">
         <v>140</v>
       </c>
-      <c r="F216" s="79"/>
-      <c r="G216" s="80"/>
-      <c r="H216" s="69"/>
-      <c r="I216" s="70"/>
-      <c r="J216" s="73"/>
-      <c r="K216" s="74"/>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A217" s="53"/>
-      <c r="B217" s="53"/>
-      <c r="C217" s="53"/>
-      <c r="D217" s="53"/>
-      <c r="E217" s="53"/>
-      <c r="F217" s="53"/>
-      <c r="G217" s="53"/>
-      <c r="H217" s="53"/>
-      <c r="I217" s="53"/>
-      <c r="J217" s="53"/>
-      <c r="K217" s="53"/>
-    </row>
-    <row r="218" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="53"/>
-      <c r="B218" s="53"/>
-      <c r="C218" s="53"/>
-      <c r="D218" s="53"/>
-      <c r="E218" s="53"/>
-      <c r="F218" s="53"/>
-      <c r="G218" s="53"/>
-      <c r="H218" s="53"/>
-      <c r="I218" s="53"/>
-      <c r="J218" s="53"/>
-      <c r="K218" s="53"/>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A219" s="54" t="s">
+      <c r="F216" s="81"/>
+      <c r="G216" s="82"/>
+      <c r="H216" s="71"/>
+      <c r="I216" s="72"/>
+      <c r="J216" s="75"/>
+      <c r="K216" s="76"/>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A217" s="65"/>
+      <c r="B217" s="65"/>
+      <c r="C217" s="65"/>
+      <c r="D217" s="65"/>
+      <c r="E217" s="65"/>
+      <c r="F217" s="65"/>
+      <c r="G217" s="65"/>
+      <c r="H217" s="65"/>
+      <c r="I217" s="65"/>
+      <c r="J217" s="65"/>
+      <c r="K217" s="65"/>
+    </row>
+    <row r="218" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="65"/>
+      <c r="B218" s="65"/>
+      <c r="C218" s="65"/>
+      <c r="D218" s="65"/>
+      <c r="E218" s="65"/>
+      <c r="F218" s="65"/>
+      <c r="G218" s="65"/>
+      <c r="H218" s="65"/>
+      <c r="I218" s="65"/>
+      <c r="J218" s="65"/>
+      <c r="K218" s="65"/>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A219" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B219" s="54"/>
-      <c r="C219" s="54"/>
-      <c r="D219" s="54"/>
-      <c r="E219" s="54"/>
-      <c r="F219" s="54"/>
-      <c r="G219" s="54"/>
-      <c r="H219" s="54"/>
-      <c r="I219" s="54"/>
-      <c r="J219" s="54"/>
-      <c r="K219" s="54"/>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A220" s="54"/>
-      <c r="B220" s="54"/>
-      <c r="C220" s="54"/>
-      <c r="D220" s="54"/>
-      <c r="E220" s="54"/>
-      <c r="F220" s="54"/>
-      <c r="G220" s="54"/>
-      <c r="H220" s="54"/>
-      <c r="I220" s="54"/>
-      <c r="J220" s="54"/>
-      <c r="K220" s="54"/>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A221" s="54"/>
-      <c r="B221" s="54"/>
-      <c r="C221" s="54"/>
-      <c r="D221" s="54"/>
-      <c r="E221" s="54"/>
-      <c r="F221" s="54"/>
-      <c r="G221" s="54"/>
-      <c r="H221" s="54"/>
-      <c r="I221" s="54"/>
-      <c r="J221" s="54"/>
-      <c r="K221" s="54"/>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A222" s="54"/>
-      <c r="B222" s="54"/>
-      <c r="C222" s="54"/>
-      <c r="D222" s="54"/>
-      <c r="E222" s="54"/>
-      <c r="F222" s="54"/>
-      <c r="G222" s="54"/>
-      <c r="H222" s="54"/>
-      <c r="I222" s="54"/>
-      <c r="J222" s="54"/>
-      <c r="K222" s="54"/>
-    </row>
-    <row r="223" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C224" s="55"/>
-      <c r="D224" s="56"/>
-      <c r="E224" s="56"/>
-      <c r="F224" s="56"/>
-      <c r="G224" s="56"/>
-      <c r="H224" s="56"/>
-      <c r="I224" s="57"/>
-    </row>
-    <row r="225" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C225" s="58"/>
-      <c r="D225" s="59"/>
-      <c r="E225" s="59"/>
-      <c r="F225" s="59"/>
-      <c r="G225" s="59"/>
-      <c r="H225" s="59"/>
-      <c r="I225" s="60"/>
-    </row>
-    <row r="226" spans="3:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C226" s="61"/>
-      <c r="D226" s="62"/>
-      <c r="E226" s="62"/>
-      <c r="F226" s="62"/>
-      <c r="G226" s="62"/>
-      <c r="H226" s="62"/>
-      <c r="I226" s="63"/>
-    </row>
-    <row r="227" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B219" s="55"/>
+      <c r="C219" s="55"/>
+      <c r="D219" s="55"/>
+      <c r="E219" s="55"/>
+      <c r="F219" s="55"/>
+      <c r="G219" s="55"/>
+      <c r="H219" s="55"/>
+      <c r="I219" s="55"/>
+      <c r="J219" s="55"/>
+      <c r="K219" s="55"/>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A220" s="55"/>
+      <c r="B220" s="55"/>
+      <c r="C220" s="55"/>
+      <c r="D220" s="55"/>
+      <c r="E220" s="55"/>
+      <c r="F220" s="55"/>
+      <c r="G220" s="55"/>
+      <c r="H220" s="55"/>
+      <c r="I220" s="55"/>
+      <c r="J220" s="55"/>
+      <c r="K220" s="55"/>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A221" s="55"/>
+      <c r="B221" s="55"/>
+      <c r="C221" s="55"/>
+      <c r="D221" s="55"/>
+      <c r="E221" s="55"/>
+      <c r="F221" s="55"/>
+      <c r="G221" s="55"/>
+      <c r="H221" s="55"/>
+      <c r="I221" s="55"/>
+      <c r="J221" s="55"/>
+      <c r="K221" s="55"/>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A222" s="55"/>
+      <c r="B222" s="55"/>
+      <c r="C222" s="55"/>
+      <c r="D222" s="55"/>
+      <c r="E222" s="55"/>
+      <c r="F222" s="55"/>
+      <c r="G222" s="55"/>
+      <c r="H222" s="55"/>
+      <c r="I222" s="55"/>
+      <c r="J222" s="55"/>
+      <c r="K222" s="55"/>
+    </row>
+    <row r="223" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C224" s="56"/>
+      <c r="D224" s="57"/>
+      <c r="E224" s="57"/>
+      <c r="F224" s="57"/>
+      <c r="G224" s="57"/>
+      <c r="H224" s="57"/>
+      <c r="I224" s="58"/>
+    </row>
+    <row r="225" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C225" s="59"/>
+      <c r="D225" s="60"/>
+      <c r="E225" s="60"/>
+      <c r="F225" s="60"/>
+      <c r="G225" s="60"/>
+      <c r="H225" s="60"/>
+      <c r="I225" s="61"/>
+    </row>
+    <row r="226" spans="3:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C226" s="62"/>
+      <c r="D226" s="63"/>
+      <c r="E226" s="63"/>
+      <c r="F226" s="63"/>
+      <c r="G226" s="63"/>
+      <c r="H226" s="63"/>
+      <c r="I226" s="64"/>
+    </row>
+    <row r="227" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I227" s="3"/>
     </row>
-    <row r="228" spans="3:18" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="3:18" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I228" s="3"/>
       <c r="N228">
         <v>366</v>
@@ -8375,7 +8375,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="229" spans="3:18" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:18" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C229" s="4" t="s">
         <v>0</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="230" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="230" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C230" s="7">
         <v>348</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="231" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="231" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C231" s="7">
         <v>349</v>
       </c>
@@ -8489,7 +8489,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="232" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="232" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C232" s="7">
         <v>350</v>
       </c>
@@ -8527,7 +8527,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="233" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="233" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C233" s="7">
         <v>351</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="234" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="234" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C234" s="11">
         <v>352</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="235" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="235" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C235" s="11">
         <v>353</v>
       </c>
@@ -8641,7 +8641,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="236" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="236" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C236" s="11">
         <v>354</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="237" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="237" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C237" s="11">
         <v>355</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="238" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="238" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C238" s="11">
         <v>356</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="239" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="239" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C239" s="11">
         <v>357</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="240" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="240" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C240" s="11">
         <v>358</v>
       </c>
@@ -8831,7 +8831,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="241" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="241" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C241" s="11">
         <v>359</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="242" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="242" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C242" s="11">
         <v>360</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="243" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="243" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C243" s="11">
         <v>361</v>
       </c>
@@ -8945,7 +8945,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="244" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="244" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C244" s="11">
         <v>362</v>
       </c>
@@ -8983,7 +8983,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="245" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="245" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C245" s="11">
         <v>363</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="246" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="246" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C246" s="11">
         <v>364</v>
       </c>
@@ -9059,7 +9059,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="247" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="247" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C247" s="11">
         <v>365</v>
       </c>
@@ -9097,7 +9097,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="248" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="248" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C248" s="11">
         <v>2007</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="249" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="249" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C249" s="11">
         <v>2008</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="250" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="250" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C250" s="11">
         <v>2009</v>
       </c>
@@ -9211,7 +9211,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="251" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="251" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C251" s="11">
         <v>2010</v>
       </c>
@@ -9249,7 +9249,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="252" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="252" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C252" s="11">
         <v>2011</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="253" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="253" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C253" s="11">
         <v>2012</v>
       </c>
@@ -9325,7 +9325,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="254" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="254" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C254" s="11">
         <v>2013</v>
       </c>
@@ -9363,7 +9363,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="255" spans="3:18" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="3:18" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C255" s="15">
         <v>2006</v>
       </c>
@@ -9386,253 +9386,253 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="3:18" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="256" spans="3:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I256" s="3"/>
     </row>
-    <row r="257" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="257" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I257" s="3"/>
     </row>
-    <row r="258" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="258" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I258" s="3"/>
     </row>
-    <row r="259" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="259" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I259" s="3"/>
     </row>
-    <row r="260" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="260" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I260" s="3"/>
     </row>
-    <row r="261" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="261" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I261" s="3"/>
     </row>
-    <row r="262" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="262" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I262" s="3"/>
     </row>
-    <row r="263" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="263" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I263" s="3"/>
     </row>
-    <row r="264" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="264" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I264" s="3"/>
     </row>
-    <row r="265" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="265" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I265" s="3"/>
     </row>
-    <row r="266" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="266" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I266" s="3"/>
     </row>
-    <row r="267" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="267" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I267" s="3"/>
     </row>
-    <row r="268" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="268" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I268" s="3"/>
     </row>
-    <row r="269" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="269" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I269" s="3"/>
     </row>
-    <row r="270" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="270" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I270" s="3"/>
     </row>
-    <row r="271" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="271" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I271" s="3"/>
     </row>
-    <row r="272" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="272" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I272" s="3"/>
     </row>
-    <row r="273" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="273" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I273" s="3"/>
     </row>
-    <row r="274" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="274" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I274" s="3"/>
     </row>
-    <row r="275" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="275" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I275" s="3"/>
     </row>
-    <row r="276" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="276" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I276" s="3"/>
     </row>
-    <row r="277" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="277" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I277" s="3"/>
     </row>
-    <row r="278" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="278" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I278" s="3"/>
     </row>
-    <row r="279" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="279" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I279" s="3"/>
     </row>
-    <row r="280" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="280" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I280" s="3"/>
     </row>
-    <row r="281" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="281" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I281" s="3"/>
     </row>
-    <row r="282" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="282" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I282" s="3"/>
     </row>
-    <row r="283" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="283" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I283" s="3"/>
     </row>
-    <row r="284" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="284" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I284" s="3"/>
     </row>
-    <row r="285" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="285" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I285" s="3"/>
     </row>
-    <row r="286" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="286" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I286" s="3"/>
     </row>
-    <row r="287" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="287" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I287" s="3"/>
     </row>
-    <row r="288" spans="9:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="9:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I288" s="3"/>
     </row>
-    <row r="289" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
       <c r="D289" s="2"/>
-      <c r="E289" s="64" t="s">
+      <c r="E289" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F289" s="65"/>
-      <c r="G289" s="66"/>
-      <c r="H289" s="67" t="s">
+      <c r="F289" s="67"/>
+      <c r="G289" s="68"/>
+      <c r="H289" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I289" s="68"/>
-      <c r="J289" s="71"/>
-      <c r="K289" s="72"/>
-    </row>
-    <row r="290" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A290" s="75" t="s">
+      <c r="I289" s="70"/>
+      <c r="J289" s="73"/>
+      <c r="K289" s="74"/>
+    </row>
+    <row r="290" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A290" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B290" s="76"/>
-      <c r="C290" s="76"/>
-      <c r="D290" s="77"/>
-      <c r="E290" s="78">
+      <c r="B290" s="78"/>
+      <c r="C290" s="78"/>
+      <c r="D290" s="79"/>
+      <c r="E290" s="80">
         <v>140</v>
       </c>
-      <c r="F290" s="79"/>
-      <c r="G290" s="80"/>
-      <c r="H290" s="69"/>
-      <c r="I290" s="70"/>
-      <c r="J290" s="73"/>
-      <c r="K290" s="74"/>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A291" s="53"/>
-      <c r="B291" s="53"/>
-      <c r="C291" s="53"/>
-      <c r="D291" s="53"/>
-      <c r="E291" s="53"/>
-      <c r="F291" s="53"/>
-      <c r="G291" s="53"/>
-      <c r="H291" s="53"/>
-      <c r="I291" s="53"/>
-      <c r="J291" s="53"/>
-      <c r="K291" s="53"/>
-    </row>
-    <row r="292" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="53"/>
-      <c r="B292" s="53"/>
-      <c r="C292" s="53"/>
-      <c r="D292" s="53"/>
-      <c r="E292" s="53"/>
-      <c r="F292" s="53"/>
-      <c r="G292" s="53"/>
-      <c r="H292" s="53"/>
-      <c r="I292" s="53"/>
-      <c r="J292" s="53"/>
-      <c r="K292" s="53"/>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A293" s="54" t="s">
+      <c r="F290" s="81"/>
+      <c r="G290" s="82"/>
+      <c r="H290" s="71"/>
+      <c r="I290" s="72"/>
+      <c r="J290" s="75"/>
+      <c r="K290" s="76"/>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A291" s="65"/>
+      <c r="B291" s="65"/>
+      <c r="C291" s="65"/>
+      <c r="D291" s="65"/>
+      <c r="E291" s="65"/>
+      <c r="F291" s="65"/>
+      <c r="G291" s="65"/>
+      <c r="H291" s="65"/>
+      <c r="I291" s="65"/>
+      <c r="J291" s="65"/>
+      <c r="K291" s="65"/>
+    </row>
+    <row r="292" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A292" s="65"/>
+      <c r="B292" s="65"/>
+      <c r="C292" s="65"/>
+      <c r="D292" s="65"/>
+      <c r="E292" s="65"/>
+      <c r="F292" s="65"/>
+      <c r="G292" s="65"/>
+      <c r="H292" s="65"/>
+      <c r="I292" s="65"/>
+      <c r="J292" s="65"/>
+      <c r="K292" s="65"/>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A293" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B293" s="54"/>
-      <c r="C293" s="54"/>
-      <c r="D293" s="54"/>
-      <c r="E293" s="54"/>
-      <c r="F293" s="54"/>
-      <c r="G293" s="54"/>
-      <c r="H293" s="54"/>
-      <c r="I293" s="54"/>
-      <c r="J293" s="54"/>
-      <c r="K293" s="54"/>
-    </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A294" s="54"/>
-      <c r="B294" s="54"/>
-      <c r="C294" s="54"/>
-      <c r="D294" s="54"/>
-      <c r="E294" s="54"/>
-      <c r="F294" s="54"/>
-      <c r="G294" s="54"/>
-      <c r="H294" s="54"/>
-      <c r="I294" s="54"/>
-      <c r="J294" s="54"/>
-      <c r="K294" s="54"/>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A295" s="54"/>
-      <c r="B295" s="54"/>
-      <c r="C295" s="54"/>
-      <c r="D295" s="54"/>
-      <c r="E295" s="54"/>
-      <c r="F295" s="54"/>
-      <c r="G295" s="54"/>
-      <c r="H295" s="54"/>
-      <c r="I295" s="54"/>
-      <c r="J295" s="54"/>
-      <c r="K295" s="54"/>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A296" s="54"/>
-      <c r="B296" s="54"/>
-      <c r="C296" s="54"/>
-      <c r="D296" s="54"/>
-      <c r="E296" s="54"/>
-      <c r="F296" s="54"/>
-      <c r="G296" s="54"/>
-      <c r="H296" s="54"/>
-      <c r="I296" s="54"/>
-      <c r="J296" s="54"/>
-      <c r="K296" s="54"/>
-    </row>
-    <row r="297" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C298" s="55"/>
-      <c r="D298" s="56"/>
-      <c r="E298" s="56"/>
-      <c r="F298" s="56"/>
-      <c r="G298" s="56"/>
-      <c r="H298" s="56"/>
-      <c r="I298" s="57"/>
-    </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C299" s="58"/>
-      <c r="D299" s="59"/>
-      <c r="E299" s="59"/>
-      <c r="F299" s="59"/>
-      <c r="G299" s="59"/>
-      <c r="H299" s="59"/>
-      <c r="I299" s="60"/>
-    </row>
-    <row r="300" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C300" s="61"/>
-      <c r="D300" s="62"/>
-      <c r="E300" s="62"/>
-      <c r="F300" s="62"/>
-      <c r="G300" s="62"/>
-      <c r="H300" s="62"/>
-      <c r="I300" s="63"/>
-    </row>
-    <row r="301" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B293" s="55"/>
+      <c r="C293" s="55"/>
+      <c r="D293" s="55"/>
+      <c r="E293" s="55"/>
+      <c r="F293" s="55"/>
+      <c r="G293" s="55"/>
+      <c r="H293" s="55"/>
+      <c r="I293" s="55"/>
+      <c r="J293" s="55"/>
+      <c r="K293" s="55"/>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A294" s="55"/>
+      <c r="B294" s="55"/>
+      <c r="C294" s="55"/>
+      <c r="D294" s="55"/>
+      <c r="E294" s="55"/>
+      <c r="F294" s="55"/>
+      <c r="G294" s="55"/>
+      <c r="H294" s="55"/>
+      <c r="I294" s="55"/>
+      <c r="J294" s="55"/>
+      <c r="K294" s="55"/>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A295" s="55"/>
+      <c r="B295" s="55"/>
+      <c r="C295" s="55"/>
+      <c r="D295" s="55"/>
+      <c r="E295" s="55"/>
+      <c r="F295" s="55"/>
+      <c r="G295" s="55"/>
+      <c r="H295" s="55"/>
+      <c r="I295" s="55"/>
+      <c r="J295" s="55"/>
+      <c r="K295" s="55"/>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A296" s="55"/>
+      <c r="B296" s="55"/>
+      <c r="C296" s="55"/>
+      <c r="D296" s="55"/>
+      <c r="E296" s="55"/>
+      <c r="F296" s="55"/>
+      <c r="G296" s="55"/>
+      <c r="H296" s="55"/>
+      <c r="I296" s="55"/>
+      <c r="J296" s="55"/>
+      <c r="K296" s="55"/>
+    </row>
+    <row r="297" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C298" s="56"/>
+      <c r="D298" s="57"/>
+      <c r="E298" s="57"/>
+      <c r="F298" s="57"/>
+      <c r="G298" s="57"/>
+      <c r="H298" s="57"/>
+      <c r="I298" s="58"/>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C299" s="59"/>
+      <c r="D299" s="60"/>
+      <c r="E299" s="60"/>
+      <c r="F299" s="60"/>
+      <c r="G299" s="60"/>
+      <c r="H299" s="60"/>
+      <c r="I299" s="61"/>
+    </row>
+    <row r="300" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C300" s="62"/>
+      <c r="D300" s="63"/>
+      <c r="E300" s="63"/>
+      <c r="F300" s="63"/>
+      <c r="G300" s="63"/>
+      <c r="H300" s="63"/>
+      <c r="I300" s="64"/>
+    </row>
+    <row r="301" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I301" s="3"/>
     </row>
-    <row r="302" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C302" s="4" t="s">
         <v>0</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C303" s="7">
         <v>366</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C304" s="7">
         <v>367</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="305" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="305" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C305" s="7">
         <v>368</v>
       </c>
@@ -9724,7 +9724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="306" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="306" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C306" s="7">
         <v>369</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="307" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="307" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C307" s="11">
         <v>370</v>
       </c>
@@ -9770,7 +9770,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="308" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="308" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C308" s="11">
         <v>371</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="309" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="309" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C309" s="11">
         <v>372</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="310" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="310" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C310" s="11">
         <v>373</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="311" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="311" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C311" s="11">
         <v>374</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="312" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="312" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C312" s="11">
         <v>375</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="313" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="313" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C313" s="11">
         <v>376</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="314" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="314" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C314" s="11">
         <v>377</v>
       </c>
@@ -9931,7 +9931,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="315" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="315" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C315" s="11">
         <v>378</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="316" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="316" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C316" s="11">
         <v>379</v>
       </c>
@@ -9977,7 +9977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="317" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="317" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C317" s="11">
         <v>380</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="318" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="318" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C318" s="11">
         <v>381</v>
       </c>
@@ -10023,7 +10023,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="319" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="319" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C319" s="11">
         <v>382</v>
       </c>
@@ -10046,7 +10046,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="320" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="320" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C320" s="11">
         <v>383</v>
       </c>
@@ -10069,7 +10069,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="321" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="321" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C321" s="11">
         <v>384</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="322" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="322" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C322" s="11">
         <v>385</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="323" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="323" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C323" s="11">
         <v>386</v>
       </c>
@@ -10138,7 +10138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="324" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="324" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C324" s="11">
         <v>387</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="325" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="325" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C325" s="11">
         <v>388</v>
       </c>
@@ -10184,7 +10184,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="326" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="326" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C326" s="11">
         <v>389</v>
       </c>
@@ -10207,7 +10207,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="327" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="327" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C327" s="11">
         <v>390</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="328" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="328" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C328" s="11">
         <v>391</v>
       </c>
@@ -10253,7 +10253,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="329" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C329" s="15">
         <v>392</v>
       </c>
@@ -10276,247 +10276,247 @@
         <v>13</v>
       </c>
     </row>
-    <row r="330" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="330" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I330" s="3"/>
     </row>
-    <row r="331" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="331" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I331" s="3"/>
     </row>
-    <row r="332" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="332" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I332" s="3"/>
     </row>
-    <row r="333" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="333" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I333" s="3"/>
     </row>
-    <row r="334" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="334" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I334" s="3"/>
     </row>
-    <row r="335" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="335" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I335" s="3"/>
     </row>
-    <row r="336" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="336" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I336" s="3"/>
     </row>
-    <row r="337" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="337" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I337" s="3"/>
     </row>
-    <row r="338" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="338" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I338" s="3"/>
     </row>
-    <row r="339" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="339" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I339" s="3"/>
     </row>
-    <row r="340" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="340" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I340" s="3"/>
     </row>
-    <row r="341" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="341" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I341" s="3"/>
     </row>
-    <row r="342" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="342" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I342" s="3"/>
     </row>
-    <row r="343" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="343" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I343" s="3"/>
     </row>
-    <row r="344" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="344" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I344" s="3"/>
     </row>
-    <row r="345" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="345" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I345" s="3"/>
     </row>
-    <row r="346" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="346" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I346" s="3"/>
     </row>
-    <row r="347" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="347" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I347" s="3"/>
     </row>
-    <row r="348" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="348" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I348" s="3"/>
     </row>
-    <row r="349" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="349" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I349" s="3"/>
     </row>
-    <row r="350" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="350" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I350" s="3"/>
     </row>
-    <row r="351" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="351" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I351" s="3"/>
     </row>
-    <row r="352" spans="9:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="352" spans="9:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I352" s="3"/>
     </row>
-    <row r="353" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I353" s="3"/>
     </row>
-    <row r="354" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I354" s="3"/>
     </row>
-    <row r="355" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I355" s="3"/>
     </row>
-    <row r="356" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I356" s="3"/>
     </row>
-    <row r="357" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I357" s="3"/>
     </row>
-    <row r="358" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I358" s="3"/>
     </row>
-    <row r="359" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I359" s="3"/>
     </row>
-    <row r="360" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
       <c r="D360" s="2"/>
-      <c r="E360" s="64" t="s">
+      <c r="E360" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F360" s="65"/>
-      <c r="G360" s="66"/>
-      <c r="H360" s="67" t="s">
+      <c r="F360" s="67"/>
+      <c r="G360" s="68"/>
+      <c r="H360" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I360" s="68"/>
-      <c r="J360" s="71"/>
-      <c r="K360" s="72"/>
-    </row>
-    <row r="361" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A361" s="75" t="s">
+      <c r="I360" s="70"/>
+      <c r="J360" s="73"/>
+      <c r="K360" s="74"/>
+    </row>
+    <row r="361" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A361" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B361" s="76"/>
-      <c r="C361" s="76"/>
-      <c r="D361" s="77"/>
-      <c r="E361" s="78">
+      <c r="B361" s="78"/>
+      <c r="C361" s="78"/>
+      <c r="D361" s="79"/>
+      <c r="E361" s="80">
         <v>140</v>
       </c>
-      <c r="F361" s="79"/>
-      <c r="G361" s="80"/>
-      <c r="H361" s="69"/>
-      <c r="I361" s="70"/>
-      <c r="J361" s="73"/>
-      <c r="K361" s="74"/>
-    </row>
-    <row r="362" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="F361" s="81"/>
+      <c r="G361" s="82"/>
+      <c r="H361" s="71"/>
+      <c r="I361" s="72"/>
+      <c r="J361" s="75"/>
+      <c r="K361" s="76"/>
+    </row>
+    <row r="362" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="I362" s="3"/>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A363" s="53"/>
-      <c r="B363" s="53"/>
-      <c r="C363" s="53"/>
-      <c r="D363" s="53"/>
-      <c r="E363" s="53"/>
-      <c r="F363" s="53"/>
-      <c r="G363" s="53"/>
-      <c r="H363" s="53"/>
-      <c r="I363" s="53"/>
-      <c r="J363" s="53"/>
-      <c r="K363" s="53"/>
-    </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A364" s="53"/>
-      <c r="B364" s="53"/>
-      <c r="C364" s="53"/>
-      <c r="D364" s="53"/>
-      <c r="E364" s="53"/>
-      <c r="F364" s="53"/>
-      <c r="G364" s="53"/>
-      <c r="H364" s="53"/>
-      <c r="I364" s="53"/>
-      <c r="J364" s="53"/>
-      <c r="K364" s="53"/>
-    </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A365" s="54" t="s">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A363" s="65"/>
+      <c r="B363" s="65"/>
+      <c r="C363" s="65"/>
+      <c r="D363" s="65"/>
+      <c r="E363" s="65"/>
+      <c r="F363" s="65"/>
+      <c r="G363" s="65"/>
+      <c r="H363" s="65"/>
+      <c r="I363" s="65"/>
+      <c r="J363" s="65"/>
+      <c r="K363" s="65"/>
+    </row>
+    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A364" s="65"/>
+      <c r="B364" s="65"/>
+      <c r="C364" s="65"/>
+      <c r="D364" s="65"/>
+      <c r="E364" s="65"/>
+      <c r="F364" s="65"/>
+      <c r="G364" s="65"/>
+      <c r="H364" s="65"/>
+      <c r="I364" s="65"/>
+      <c r="J364" s="65"/>
+      <c r="K364" s="65"/>
+    </row>
+    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A365" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B365" s="54"/>
-      <c r="C365" s="54"/>
-      <c r="D365" s="54"/>
-      <c r="E365" s="54"/>
-      <c r="F365" s="54"/>
-      <c r="G365" s="54"/>
-      <c r="H365" s="54"/>
-      <c r="I365" s="54"/>
-      <c r="J365" s="54"/>
-      <c r="K365" s="54"/>
-    </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A366" s="54"/>
-      <c r="B366" s="54"/>
-      <c r="C366" s="54"/>
-      <c r="D366" s="54"/>
-      <c r="E366" s="54"/>
-      <c r="F366" s="54"/>
-      <c r="G366" s="54"/>
-      <c r="H366" s="54"/>
-      <c r="I366" s="54"/>
-      <c r="J366" s="54"/>
-      <c r="K366" s="54"/>
-    </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A367" s="54"/>
-      <c r="B367" s="54"/>
-      <c r="C367" s="54"/>
-      <c r="D367" s="54"/>
-      <c r="E367" s="54"/>
-      <c r="F367" s="54"/>
-      <c r="G367" s="54"/>
-      <c r="H367" s="54"/>
-      <c r="I367" s="54"/>
-      <c r="J367" s="54"/>
-      <c r="K367" s="54"/>
-    </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A368" s="54"/>
-      <c r="B368" s="54"/>
-      <c r="C368" s="54"/>
-      <c r="D368" s="54"/>
-      <c r="E368" s="54"/>
-      <c r="F368" s="54"/>
-      <c r="G368" s="54"/>
-      <c r="H368" s="54"/>
-      <c r="I368" s="54"/>
-      <c r="J368" s="54"/>
-      <c r="K368" s="54"/>
-    </row>
-    <row r="369" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="370" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C370" s="55"/>
-      <c r="D370" s="56"/>
-      <c r="E370" s="56"/>
-      <c r="F370" s="56"/>
-      <c r="G370" s="56"/>
-      <c r="H370" s="56"/>
-      <c r="I370" s="57"/>
-    </row>
-    <row r="371" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C371" s="58"/>
-      <c r="D371" s="59"/>
-      <c r="E371" s="59"/>
-      <c r="F371" s="59"/>
-      <c r="G371" s="59"/>
-      <c r="H371" s="59"/>
-      <c r="I371" s="60"/>
-    </row>
-    <row r="372" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C372" s="61"/>
-      <c r="D372" s="62"/>
-      <c r="E372" s="62"/>
-      <c r="F372" s="62"/>
-      <c r="G372" s="62"/>
-      <c r="H372" s="62"/>
-      <c r="I372" s="63"/>
-    </row>
-    <row r="373" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B365" s="55"/>
+      <c r="C365" s="55"/>
+      <c r="D365" s="55"/>
+      <c r="E365" s="55"/>
+      <c r="F365" s="55"/>
+      <c r="G365" s="55"/>
+      <c r="H365" s="55"/>
+      <c r="I365" s="55"/>
+      <c r="J365" s="55"/>
+      <c r="K365" s="55"/>
+    </row>
+    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A366" s="55"/>
+      <c r="B366" s="55"/>
+      <c r="C366" s="55"/>
+      <c r="D366" s="55"/>
+      <c r="E366" s="55"/>
+      <c r="F366" s="55"/>
+      <c r="G366" s="55"/>
+      <c r="H366" s="55"/>
+      <c r="I366" s="55"/>
+      <c r="J366" s="55"/>
+      <c r="K366" s="55"/>
+    </row>
+    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A367" s="55"/>
+      <c r="B367" s="55"/>
+      <c r="C367" s="55"/>
+      <c r="D367" s="55"/>
+      <c r="E367" s="55"/>
+      <c r="F367" s="55"/>
+      <c r="G367" s="55"/>
+      <c r="H367" s="55"/>
+      <c r="I367" s="55"/>
+      <c r="J367" s="55"/>
+      <c r="K367" s="55"/>
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A368" s="55"/>
+      <c r="B368" s="55"/>
+      <c r="C368" s="55"/>
+      <c r="D368" s="55"/>
+      <c r="E368" s="55"/>
+      <c r="F368" s="55"/>
+      <c r="G368" s="55"/>
+      <c r="H368" s="55"/>
+      <c r="I368" s="55"/>
+      <c r="J368" s="55"/>
+      <c r="K368" s="55"/>
+    </row>
+    <row r="369" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="370" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C370" s="56"/>
+      <c r="D370" s="57"/>
+      <c r="E370" s="57"/>
+      <c r="F370" s="57"/>
+      <c r="G370" s="57"/>
+      <c r="H370" s="57"/>
+      <c r="I370" s="58"/>
+    </row>
+    <row r="371" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C371" s="59"/>
+      <c r="D371" s="60"/>
+      <c r="E371" s="60"/>
+      <c r="F371" s="60"/>
+      <c r="G371" s="60"/>
+      <c r="H371" s="60"/>
+      <c r="I371" s="61"/>
+    </row>
+    <row r="372" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C372" s="62"/>
+      <c r="D372" s="63"/>
+      <c r="E372" s="63"/>
+      <c r="F372" s="63"/>
+      <c r="G372" s="63"/>
+      <c r="H372" s="63"/>
+      <c r="I372" s="64"/>
+    </row>
+    <row r="373" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I373" s="3"/>
     </row>
-    <row r="374" spans="3:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="374" spans="3:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C374" s="4" t="s">
         <v>0</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="375" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="375" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C375" s="7">
         <v>2014</v>
       </c>
@@ -10562,7 +10562,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="376" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="376" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C376" s="7">
         <v>2015</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="377" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="377" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C377" s="7">
         <v>2016</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="378" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="378" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C378" s="7">
         <v>2017</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="379" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="379" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C379" s="11">
         <v>2018</v>
       </c>
@@ -10654,7 +10654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="380" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="380" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C380" s="11">
         <v>2019</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="381" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="381" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C381" s="11">
         <v>2020</v>
       </c>
@@ -10700,7 +10700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="382" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="382" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C382" s="11">
         <v>2021</v>
       </c>
@@ -10723,7 +10723,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="383" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="383" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C383" s="11">
         <v>2022</v>
       </c>
@@ -10746,7 +10746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="384" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="384" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C384" s="11">
         <v>2023</v>
       </c>
@@ -10769,7 +10769,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="385" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="385" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C385" s="11">
         <v>2024</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="386" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="386" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C386" s="11">
         <v>2025</v>
       </c>
@@ -10815,7 +10815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="387" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="387" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C387" s="11">
         <v>2026</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="388" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="388" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C388" s="11">
         <v>2027</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="389" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="389" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C389" s="11">
         <v>2028</v>
       </c>
@@ -10884,7 +10884,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="390" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="390" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C390" s="11">
         <v>2029</v>
       </c>
@@ -10907,7 +10907,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="391" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="391" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C391" s="11">
         <v>2030</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="392" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="392" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C392" s="11">
         <v>2031</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="393" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="393" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C393" s="11">
         <v>2032</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="394" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="394" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C394" s="11">
         <v>2033</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="395" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="395" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C395" s="11">
         <v>2034</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="396" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="396" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C396" s="11">
         <v>2035</v>
       </c>
@@ -11045,7 +11045,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="397" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="397" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C397" s="11">
         <v>2036</v>
       </c>
@@ -11068,7 +11068,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="398" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="398" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C398" s="11">
         <v>2037</v>
       </c>
@@ -11091,7 +11091,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="399" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="399" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C399" s="11">
         <v>2038</v>
       </c>
@@ -11114,7 +11114,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="400" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="400" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C400" s="11">
         <v>2039</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="401" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="401" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C401" s="11">
         <v>2040</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="402" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="402" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C402" s="11">
         <v>2041</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="403" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="403" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C403" s="11">
         <v>2042</v>
       </c>
@@ -11206,7 +11206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="404" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="404" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C404" s="11">
         <v>2043</v>
       </c>
@@ -11229,7 +11229,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="405" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="405" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C405" s="11">
         <v>2044</v>
       </c>
@@ -11252,7 +11252,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="406" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="406" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C406" s="11">
         <v>2045</v>
       </c>
@@ -11275,7 +11275,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="407" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="407" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C407" s="11">
         <v>2046</v>
       </c>
@@ -11298,7 +11298,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="408" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="408" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C408" s="11">
         <v>2047</v>
       </c>
@@ -11321,7 +11321,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="409" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="409" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C409" s="11">
         <v>2048</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="410" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="410" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C410" s="11">
         <v>2049</v>
       </c>
@@ -11367,7 +11367,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="411" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="411" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C411" s="11">
         <v>2050</v>
       </c>
@@ -11390,7 +11390,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="412" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="412" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C412" s="11">
         <v>2051</v>
       </c>
@@ -11413,7 +11413,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="413" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="413" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C413" s="11">
         <v>2052</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="414" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="414" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C414" s="11">
         <v>2053</v>
       </c>
@@ -11459,7 +11459,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="415" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="415" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C415" s="11">
         <v>2054</v>
       </c>
@@ -11482,7 +11482,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="416" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="416" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C416" s="11">
         <v>2055</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="417" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="417" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C417" s="11">
         <v>2056</v>
       </c>
@@ -11528,7 +11528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="418" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="418" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C418" s="11">
         <v>2057</v>
       </c>
@@ -11551,7 +11551,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="419" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="419" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C419" s="11">
         <v>2058</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="420" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="420" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C420" s="11">
         <v>2059</v>
       </c>
@@ -11597,7 +11597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="421" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="421" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C421" s="11">
         <v>2060</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="422" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="422" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C422" s="11">
         <v>2061</v>
       </c>
@@ -11643,7 +11643,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="423" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="423" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C423" s="11">
         <v>2062</v>
       </c>
@@ -11666,7 +11666,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="424" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="424" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C424" s="11">
         <v>2063</v>
       </c>
@@ -11689,7 +11689,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="425" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="425" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C425" s="11">
         <v>2064</v>
       </c>
@@ -11712,7 +11712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="426" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="426" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C426" s="11">
         <v>2065</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="427" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="427" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C427" s="11">
         <v>2066</v>
       </c>
@@ -11758,7 +11758,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="428" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="428" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C428" s="11">
         <v>2067</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="429" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="429" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C429" s="11">
         <v>2068</v>
       </c>
@@ -11804,7 +11804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="430" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="430" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C430" s="11">
         <v>2069</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="431" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C431" s="15">
         <v>2070</v>
       </c>
@@ -11850,7 +11850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="432" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="432" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C432" s="19"/>
       <c r="D432" s="20"/>
       <c r="E432" s="20"/>
@@ -11859,7 +11859,7 @@
       <c r="H432" s="19"/>
       <c r="I432" s="3"/>
     </row>
-    <row r="433" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C433" s="19"/>
       <c r="D433" s="20"/>
       <c r="E433" s="20"/>
@@ -11868,7 +11868,7 @@
       <c r="H433" s="19"/>
       <c r="I433" s="3"/>
     </row>
-    <row r="434" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C434" s="19"/>
       <c r="D434" s="20"/>
       <c r="E434" s="20"/>
@@ -11877,43 +11877,43 @@
       <c r="H434" s="19"/>
       <c r="I434" s="3"/>
     </row>
-    <row r="435" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A435" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
       <c r="D435" s="2"/>
-      <c r="E435" s="64" t="s">
+      <c r="E435" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F435" s="65"/>
-      <c r="G435" s="66"/>
-      <c r="H435" s="67" t="s">
+      <c r="F435" s="67"/>
+      <c r="G435" s="68"/>
+      <c r="H435" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I435" s="68"/>
-      <c r="J435" s="71"/>
-      <c r="K435" s="72"/>
-    </row>
-    <row r="436" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A436" s="75" t="s">
+      <c r="I435" s="70"/>
+      <c r="J435" s="73"/>
+      <c r="K435" s="74"/>
+    </row>
+    <row r="436" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A436" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B436" s="76"/>
-      <c r="C436" s="76"/>
-      <c r="D436" s="77"/>
-      <c r="E436" s="78">
+      <c r="B436" s="78"/>
+      <c r="C436" s="78"/>
+      <c r="D436" s="79"/>
+      <c r="E436" s="80">
         <v>140</v>
       </c>
-      <c r="F436" s="79"/>
-      <c r="G436" s="80"/>
-      <c r="H436" s="69"/>
-      <c r="I436" s="70"/>
-      <c r="J436" s="73"/>
-      <c r="K436" s="74"/>
-    </row>
-    <row r="437" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="F436" s="81"/>
+      <c r="G436" s="82"/>
+      <c r="H436" s="71"/>
+      <c r="I436" s="72"/>
+      <c r="J436" s="75"/>
+      <c r="K436" s="76"/>
+    </row>
+    <row r="437" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C437" s="19"/>
       <c r="D437" s="20"/>
       <c r="E437" s="20"/>
@@ -11922,115 +11922,115 @@
       <c r="H437" s="19"/>
       <c r="I437" s="3"/>
     </row>
-    <row r="438" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A438" s="53"/>
-      <c r="B438" s="53"/>
-      <c r="C438" s="53"/>
-      <c r="D438" s="53"/>
-      <c r="E438" s="53"/>
-      <c r="F438" s="53"/>
-      <c r="G438" s="53"/>
-      <c r="H438" s="53"/>
-      <c r="I438" s="53"/>
-      <c r="J438" s="53"/>
-      <c r="K438" s="53"/>
-    </row>
-    <row r="439" spans="1:11" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A439" s="53"/>
-      <c r="B439" s="53"/>
-      <c r="C439" s="53"/>
-      <c r="D439" s="53"/>
-      <c r="E439" s="53"/>
-      <c r="F439" s="53"/>
-      <c r="G439" s="53"/>
-      <c r="H439" s="53"/>
-      <c r="I439" s="53"/>
-      <c r="J439" s="53"/>
-      <c r="K439" s="53"/>
-    </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A440" s="54" t="s">
+    <row r="438" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A438" s="65"/>
+      <c r="B438" s="65"/>
+      <c r="C438" s="65"/>
+      <c r="D438" s="65"/>
+      <c r="E438" s="65"/>
+      <c r="F438" s="65"/>
+      <c r="G438" s="65"/>
+      <c r="H438" s="65"/>
+      <c r="I438" s="65"/>
+      <c r="J438" s="65"/>
+      <c r="K438" s="65"/>
+    </row>
+    <row r="439" spans="1:11" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A439" s="65"/>
+      <c r="B439" s="65"/>
+      <c r="C439" s="65"/>
+      <c r="D439" s="65"/>
+      <c r="E439" s="65"/>
+      <c r="F439" s="65"/>
+      <c r="G439" s="65"/>
+      <c r="H439" s="65"/>
+      <c r="I439" s="65"/>
+      <c r="J439" s="65"/>
+      <c r="K439" s="65"/>
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A440" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B440" s="54"/>
-      <c r="C440" s="54"/>
-      <c r="D440" s="54"/>
-      <c r="E440" s="54"/>
-      <c r="F440" s="54"/>
-      <c r="G440" s="54"/>
-      <c r="H440" s="54"/>
-      <c r="I440" s="54"/>
-      <c r="J440" s="54"/>
-      <c r="K440" s="54"/>
-    </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A441" s="54"/>
-      <c r="B441" s="54"/>
-      <c r="C441" s="54"/>
-      <c r="D441" s="54"/>
-      <c r="E441" s="54"/>
-      <c r="F441" s="54"/>
-      <c r="G441" s="54"/>
-      <c r="H441" s="54"/>
-      <c r="I441" s="54"/>
-      <c r="J441" s="54"/>
-      <c r="K441" s="54"/>
-    </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A442" s="54"/>
-      <c r="B442" s="54"/>
-      <c r="C442" s="54"/>
-      <c r="D442" s="54"/>
-      <c r="E442" s="54"/>
-      <c r="F442" s="54"/>
-      <c r="G442" s="54"/>
-      <c r="H442" s="54"/>
-      <c r="I442" s="54"/>
-      <c r="J442" s="54"/>
-      <c r="K442" s="54"/>
-    </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A443" s="54"/>
-      <c r="B443" s="54"/>
-      <c r="C443" s="54"/>
-      <c r="D443" s="54"/>
-      <c r="E443" s="54"/>
-      <c r="F443" s="54"/>
-      <c r="G443" s="54"/>
-      <c r="H443" s="54"/>
-      <c r="I443" s="54"/>
-      <c r="J443" s="54"/>
-      <c r="K443" s="54"/>
-    </row>
-    <row r="444" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C445" s="55"/>
-      <c r="D445" s="56"/>
-      <c r="E445" s="56"/>
-      <c r="F445" s="56"/>
-      <c r="G445" s="56"/>
-      <c r="H445" s="56"/>
-      <c r="I445" s="57"/>
-    </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C446" s="58"/>
-      <c r="D446" s="59"/>
-      <c r="E446" s="59"/>
-      <c r="F446" s="59"/>
-      <c r="G446" s="59"/>
-      <c r="H446" s="59"/>
-      <c r="I446" s="60"/>
-    </row>
-    <row r="447" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C447" s="61"/>
-      <c r="D447" s="62"/>
-      <c r="E447" s="62"/>
-      <c r="F447" s="62"/>
-      <c r="G447" s="62"/>
-      <c r="H447" s="62"/>
-      <c r="I447" s="63"/>
-    </row>
-    <row r="448" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B440" s="55"/>
+      <c r="C440" s="55"/>
+      <c r="D440" s="55"/>
+      <c r="E440" s="55"/>
+      <c r="F440" s="55"/>
+      <c r="G440" s="55"/>
+      <c r="H440" s="55"/>
+      <c r="I440" s="55"/>
+      <c r="J440" s="55"/>
+      <c r="K440" s="55"/>
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A441" s="55"/>
+      <c r="B441" s="55"/>
+      <c r="C441" s="55"/>
+      <c r="D441" s="55"/>
+      <c r="E441" s="55"/>
+      <c r="F441" s="55"/>
+      <c r="G441" s="55"/>
+      <c r="H441" s="55"/>
+      <c r="I441" s="55"/>
+      <c r="J441" s="55"/>
+      <c r="K441" s="55"/>
+    </row>
+    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A442" s="55"/>
+      <c r="B442" s="55"/>
+      <c r="C442" s="55"/>
+      <c r="D442" s="55"/>
+      <c r="E442" s="55"/>
+      <c r="F442" s="55"/>
+      <c r="G442" s="55"/>
+      <c r="H442" s="55"/>
+      <c r="I442" s="55"/>
+      <c r="J442" s="55"/>
+      <c r="K442" s="55"/>
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A443" s="55"/>
+      <c r="B443" s="55"/>
+      <c r="C443" s="55"/>
+      <c r="D443" s="55"/>
+      <c r="E443" s="55"/>
+      <c r="F443" s="55"/>
+      <c r="G443" s="55"/>
+      <c r="H443" s="55"/>
+      <c r="I443" s="55"/>
+      <c r="J443" s="55"/>
+      <c r="K443" s="55"/>
+    </row>
+    <row r="444" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C445" s="56"/>
+      <c r="D445" s="57"/>
+      <c r="E445" s="57"/>
+      <c r="F445" s="57"/>
+      <c r="G445" s="57"/>
+      <c r="H445" s="57"/>
+      <c r="I445" s="58"/>
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C446" s="59"/>
+      <c r="D446" s="60"/>
+      <c r="E446" s="60"/>
+      <c r="F446" s="60"/>
+      <c r="G446" s="60"/>
+      <c r="H446" s="60"/>
+      <c r="I446" s="61"/>
+    </row>
+    <row r="447" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C447" s="62"/>
+      <c r="D447" s="63"/>
+      <c r="E447" s="63"/>
+      <c r="F447" s="63"/>
+      <c r="G447" s="63"/>
+      <c r="H447" s="63"/>
+      <c r="I447" s="64"/>
+    </row>
+    <row r="448" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C448" s="19"/>
       <c r="D448" s="20"/>
       <c r="E448" s="20"/>
@@ -12039,7 +12039,7 @@
       <c r="H448" s="19"/>
       <c r="I448" s="3"/>
     </row>
-    <row r="449" spans="3:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="449" spans="3:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C449" s="4" t="s">
         <v>0</v>
       </c>
@@ -12062,7 +12062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="450" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="450" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C450" s="7">
         <v>393</v>
       </c>
@@ -12085,7 +12085,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="451" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="451" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C451" s="7">
         <v>394</v>
       </c>
@@ -12108,7 +12108,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="452" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="452" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C452" s="7">
         <v>395</v>
       </c>
@@ -12131,7 +12131,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="453" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="453" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C453" s="7">
         <v>396</v>
       </c>
@@ -12154,7 +12154,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="454" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="454" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C454" s="11">
         <v>397</v>
       </c>
@@ -12177,7 +12177,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="455" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="455" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C455" s="11">
         <v>398</v>
       </c>
@@ -12200,7 +12200,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="456" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="456" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C456" s="11">
         <v>399</v>
       </c>
@@ -12223,7 +12223,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="457" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="457" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C457" s="11">
         <v>400</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="458" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="458" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C458" s="11">
         <v>401</v>
       </c>
@@ -12269,7 +12269,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="459" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="459" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C459" s="11">
         <v>402</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="460" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="460" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C460" s="11">
         <v>403</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="461" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="461" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C461" s="11">
         <v>404</v>
       </c>
@@ -12338,7 +12338,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="462" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="462" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C462" s="11">
         <v>405</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="463" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="463" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C463" s="11">
         <v>406</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="464" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="464" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C464" s="11">
         <v>407</v>
       </c>
@@ -12407,7 +12407,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="465" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="465" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C465" s="11">
         <v>408</v>
       </c>
@@ -12430,7 +12430,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="466" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="466" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C466" s="11">
         <v>410</v>
       </c>
@@ -12453,7 +12453,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="467" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="467" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C467" s="11">
         <v>411</v>
       </c>
@@ -12476,7 +12476,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="468" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="468" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C468" s="11">
         <v>412</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="469" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="469" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C469" s="11">
         <v>413</v>
       </c>
@@ -12522,7 +12522,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="470" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="470" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C470" s="11">
         <v>415</v>
       </c>
@@ -12545,7 +12545,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="471" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="471" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C471" s="11">
         <v>416</v>
       </c>
@@ -12568,7 +12568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="472" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="472" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C472" s="11">
         <v>417</v>
       </c>
@@ -12591,7 +12591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="473" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="473" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C473" s="11">
         <v>418</v>
       </c>
@@ -12614,7 +12614,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="474" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="474" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C474" s="11">
         <v>419</v>
       </c>
@@ -12637,7 +12637,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="475" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="475" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C475" s="11">
         <v>420</v>
       </c>
@@ -12660,7 +12660,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="476" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="476" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C476" s="11">
         <v>421</v>
       </c>
@@ -12683,7 +12683,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="477" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="477" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C477" s="11">
         <v>422</v>
       </c>
@@ -12706,7 +12706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="478" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="478" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C478" s="11">
         <v>423</v>
       </c>
@@ -12729,7 +12729,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="479" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="479" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C479" s="11">
         <v>424</v>
       </c>
@@ -12752,7 +12752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="480" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="480" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C480" s="11">
         <v>425</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="481" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="481" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C481" s="11">
         <v>426</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="482" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="482" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C482" s="11">
         <v>427</v>
       </c>
@@ -12821,7 +12821,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="483" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="483" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C483" s="11">
         <v>428</v>
       </c>
@@ -12844,7 +12844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="484" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="484" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C484" s="11">
         <v>429</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="485" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="485" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C485" s="11">
         <v>430</v>
       </c>
@@ -12890,7 +12890,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="486" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="486" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C486" s="11">
         <v>431</v>
       </c>
@@ -12913,7 +12913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="487" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="487" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C487" s="11">
         <v>432</v>
       </c>
@@ -12936,7 +12936,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="488" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="488" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C488" s="11">
         <v>433</v>
       </c>
@@ -12959,7 +12959,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="489" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="489" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C489" s="11">
         <v>434</v>
       </c>
@@ -12982,7 +12982,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="490" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="490" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C490" s="11">
         <v>435</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="491" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="491" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C491" s="11">
         <v>436</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="492" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="492" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C492" s="11">
         <v>437</v>
       </c>
@@ -13051,7 +13051,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="493" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="493" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C493" s="11">
         <v>438</v>
       </c>
@@ -13074,7 +13074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="494" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="494" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C494" s="11">
         <v>439</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="495" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="495" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C495" s="11">
         <v>440</v>
       </c>
@@ -13120,7 +13120,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="496" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="496" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C496" s="11">
         <v>441</v>
       </c>
@@ -13143,7 +13143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="497" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C497" s="11">
         <v>442</v>
       </c>
@@ -13166,7 +13166,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="498" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C498" s="11">
         <v>443</v>
       </c>
@@ -13189,7 +13189,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="499" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C499" s="11">
         <v>444</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="500" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C500" s="11">
         <v>445</v>
       </c>
@@ -13235,7 +13235,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="501" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C501" s="11">
         <v>446</v>
       </c>
@@ -13258,7 +13258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="502" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C502" s="11">
         <v>447</v>
       </c>
@@ -13281,7 +13281,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="503" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C503" s="15">
         <v>448</v>
       </c>
@@ -13304,7 +13304,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="504" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C504" s="19"/>
       <c r="D504" s="20"/>
       <c r="E504" s="20"/>
@@ -13328,7 +13328,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="505" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C505" s="19"/>
       <c r="D505" s="20"/>
       <c r="E505" s="20"/>
@@ -13352,7 +13352,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="506" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C506" s="19"/>
       <c r="D506" s="20"/>
       <c r="E506" s="20"/>
@@ -13376,7 +13376,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="507" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C507" s="19"/>
       <c r="D507" s="20"/>
       <c r="E507" s="20"/>
@@ -13400,24 +13400,24 @@
         <v>106</v>
       </c>
     </row>
-    <row r="508" spans="1:22" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:22" ht="18" x14ac:dyDescent="0.35">
       <c r="A508" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B508" s="2"/>
       <c r="C508" s="2"/>
       <c r="D508" s="2"/>
-      <c r="E508" s="64" t="s">
+      <c r="E508" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F508" s="65"/>
-      <c r="G508" s="66"/>
-      <c r="H508" s="67" t="s">
+      <c r="F508" s="67"/>
+      <c r="G508" s="68"/>
+      <c r="H508" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I508" s="68"/>
-      <c r="J508" s="71"/>
-      <c r="K508" s="72"/>
+      <c r="I508" s="70"/>
+      <c r="J508" s="73"/>
+      <c r="K508" s="74"/>
       <c r="R508">
         <v>507</v>
       </c>
@@ -13434,22 +13434,22 @@
         <v>106</v>
       </c>
     </row>
-    <row r="509" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A509" s="75" t="s">
+    <row r="509" spans="1:22" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A509" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B509" s="76"/>
-      <c r="C509" s="76"/>
-      <c r="D509" s="77"/>
-      <c r="E509" s="78">
+      <c r="B509" s="78"/>
+      <c r="C509" s="78"/>
+      <c r="D509" s="79"/>
+      <c r="E509" s="80">
         <v>140</v>
       </c>
-      <c r="F509" s="79"/>
-      <c r="G509" s="80"/>
-      <c r="H509" s="69"/>
-      <c r="I509" s="70"/>
-      <c r="J509" s="73"/>
-      <c r="K509" s="74"/>
+      <c r="F509" s="81"/>
+      <c r="G509" s="82"/>
+      <c r="H509" s="71"/>
+      <c r="I509" s="72"/>
+      <c r="J509" s="75"/>
+      <c r="K509" s="76"/>
       <c r="R509">
         <v>508</v>
       </c>
@@ -13466,18 +13466,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="510" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A510" s="53"/>
-      <c r="B510" s="53"/>
-      <c r="C510" s="53"/>
-      <c r="D510" s="53"/>
-      <c r="E510" s="53"/>
-      <c r="F510" s="53"/>
-      <c r="G510" s="53"/>
-      <c r="H510" s="53"/>
-      <c r="I510" s="53"/>
-      <c r="J510" s="53"/>
-      <c r="K510" s="53"/>
+    <row r="510" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A510" s="65"/>
+      <c r="B510" s="65"/>
+      <c r="C510" s="65"/>
+      <c r="D510" s="65"/>
+      <c r="E510" s="65"/>
+      <c r="F510" s="65"/>
+      <c r="G510" s="65"/>
+      <c r="H510" s="65"/>
+      <c r="I510" s="65"/>
+      <c r="J510" s="65"/>
+      <c r="K510" s="65"/>
       <c r="R510">
         <v>509</v>
       </c>
@@ -13494,18 +13494,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="511" spans="1:22" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A511" s="53"/>
-      <c r="B511" s="53"/>
-      <c r="C511" s="53"/>
-      <c r="D511" s="53"/>
-      <c r="E511" s="53"/>
-      <c r="F511" s="53"/>
-      <c r="G511" s="53"/>
-      <c r="H511" s="53"/>
-      <c r="I511" s="53"/>
-      <c r="J511" s="53"/>
-      <c r="K511" s="53"/>
+    <row r="511" spans="1:22" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A511" s="65"/>
+      <c r="B511" s="65"/>
+      <c r="C511" s="65"/>
+      <c r="D511" s="65"/>
+      <c r="E511" s="65"/>
+      <c r="F511" s="65"/>
+      <c r="G511" s="65"/>
+      <c r="H511" s="65"/>
+      <c r="I511" s="65"/>
+      <c r="J511" s="65"/>
+      <c r="K511" s="65"/>
       <c r="R511">
         <v>510</v>
       </c>
@@ -13522,20 +13522,20 @@
         <v>106</v>
       </c>
     </row>
-    <row r="512" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A512" s="54" t="s">
+    <row r="512" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A512" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B512" s="54"/>
-      <c r="C512" s="54"/>
-      <c r="D512" s="54"/>
-      <c r="E512" s="54"/>
-      <c r="F512" s="54"/>
-      <c r="G512" s="54"/>
-      <c r="H512" s="54"/>
-      <c r="I512" s="54"/>
-      <c r="J512" s="54"/>
-      <c r="K512" s="54"/>
+      <c r="B512" s="55"/>
+      <c r="C512" s="55"/>
+      <c r="D512" s="55"/>
+      <c r="E512" s="55"/>
+      <c r="F512" s="55"/>
+      <c r="G512" s="55"/>
+      <c r="H512" s="55"/>
+      <c r="I512" s="55"/>
+      <c r="J512" s="55"/>
+      <c r="K512" s="55"/>
       <c r="R512">
         <v>511</v>
       </c>
@@ -13552,18 +13552,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="513" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A513" s="54"/>
-      <c r="B513" s="54"/>
-      <c r="C513" s="54"/>
-      <c r="D513" s="54"/>
-      <c r="E513" s="54"/>
-      <c r="F513" s="54"/>
-      <c r="G513" s="54"/>
-      <c r="H513" s="54"/>
-      <c r="I513" s="54"/>
-      <c r="J513" s="54"/>
-      <c r="K513" s="54"/>
+    <row r="513" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A513" s="55"/>
+      <c r="B513" s="55"/>
+      <c r="C513" s="55"/>
+      <c r="D513" s="55"/>
+      <c r="E513" s="55"/>
+      <c r="F513" s="55"/>
+      <c r="G513" s="55"/>
+      <c r="H513" s="55"/>
+      <c r="I513" s="55"/>
+      <c r="J513" s="55"/>
+      <c r="K513" s="55"/>
       <c r="R513">
         <v>512</v>
       </c>
@@ -13580,18 +13580,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="514" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A514" s="54"/>
-      <c r="B514" s="54"/>
-      <c r="C514" s="54"/>
-      <c r="D514" s="54"/>
-      <c r="E514" s="54"/>
-      <c r="F514" s="54"/>
-      <c r="G514" s="54"/>
-      <c r="H514" s="54"/>
-      <c r="I514" s="54"/>
-      <c r="J514" s="54"/>
-      <c r="K514" s="54"/>
+    <row r="514" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A514" s="55"/>
+      <c r="B514" s="55"/>
+      <c r="C514" s="55"/>
+      <c r="D514" s="55"/>
+      <c r="E514" s="55"/>
+      <c r="F514" s="55"/>
+      <c r="G514" s="55"/>
+      <c r="H514" s="55"/>
+      <c r="I514" s="55"/>
+      <c r="J514" s="55"/>
+      <c r="K514" s="55"/>
       <c r="R514">
         <v>513</v>
       </c>
@@ -13608,18 +13608,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="515" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A515" s="54"/>
-      <c r="B515" s="54"/>
-      <c r="C515" s="54"/>
-      <c r="D515" s="54"/>
-      <c r="E515" s="54"/>
-      <c r="F515" s="54"/>
-      <c r="G515" s="54"/>
-      <c r="H515" s="54"/>
-      <c r="I515" s="54"/>
-      <c r="J515" s="54"/>
-      <c r="K515" s="54"/>
+    <row r="515" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A515" s="55"/>
+      <c r="B515" s="55"/>
+      <c r="C515" s="55"/>
+      <c r="D515" s="55"/>
+      <c r="E515" s="55"/>
+      <c r="F515" s="55"/>
+      <c r="G515" s="55"/>
+      <c r="H515" s="55"/>
+      <c r="I515" s="55"/>
+      <c r="J515" s="55"/>
+      <c r="K515" s="55"/>
       <c r="R515">
         <v>514</v>
       </c>
@@ -13636,7 +13636,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="516" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R516">
         <v>515</v>
       </c>
@@ -13653,14 +13653,14 @@
         <v>106</v>
       </c>
     </row>
-    <row r="517" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C517" s="55"/>
-      <c r="D517" s="56"/>
-      <c r="E517" s="56"/>
-      <c r="F517" s="56"/>
-      <c r="G517" s="56"/>
-      <c r="H517" s="56"/>
-      <c r="I517" s="57"/>
+    <row r="517" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C517" s="56"/>
+      <c r="D517" s="57"/>
+      <c r="E517" s="57"/>
+      <c r="F517" s="57"/>
+      <c r="G517" s="57"/>
+      <c r="H517" s="57"/>
+      <c r="I517" s="58"/>
       <c r="R517">
         <v>516</v>
       </c>
@@ -13677,14 +13677,14 @@
         <v>106</v>
       </c>
     </row>
-    <row r="518" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C518" s="58"/>
-      <c r="D518" s="59"/>
-      <c r="E518" s="59"/>
-      <c r="F518" s="59"/>
-      <c r="G518" s="59"/>
-      <c r="H518" s="59"/>
-      <c r="I518" s="60"/>
+    <row r="518" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C518" s="59"/>
+      <c r="D518" s="60"/>
+      <c r="E518" s="60"/>
+      <c r="F518" s="60"/>
+      <c r="G518" s="60"/>
+      <c r="H518" s="60"/>
+      <c r="I518" s="61"/>
       <c r="R518">
         <v>517</v>
       </c>
@@ -13701,14 +13701,14 @@
         <v>106</v>
       </c>
     </row>
-    <row r="519" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C519" s="61"/>
-      <c r="D519" s="62"/>
-      <c r="E519" s="62"/>
-      <c r="F519" s="62"/>
-      <c r="G519" s="62"/>
-      <c r="H519" s="62"/>
-      <c r="I519" s="63"/>
+    <row r="519" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C519" s="62"/>
+      <c r="D519" s="63"/>
+      <c r="E519" s="63"/>
+      <c r="F519" s="63"/>
+      <c r="G519" s="63"/>
+      <c r="H519" s="63"/>
+      <c r="I519" s="64"/>
       <c r="R519">
         <v>518</v>
       </c>
@@ -13725,7 +13725,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="520" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C520" s="19"/>
       <c r="D520" s="20"/>
       <c r="E520" s="20"/>
@@ -13749,7 +13749,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="521" spans="1:22" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:22" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C521" s="4" t="s">
         <v>0</v>
       </c>
@@ -13787,7 +13787,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="522" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C522" s="7">
         <v>449</v>
       </c>
@@ -13825,7 +13825,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="523" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C523" s="7">
         <v>450</v>
       </c>
@@ -13863,7 +13863,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="524" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C524" s="7">
         <v>451</v>
       </c>
@@ -13901,7 +13901,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="525" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C525" s="7">
         <v>452</v>
       </c>
@@ -13939,7 +13939,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="526" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C526" s="7">
         <v>453</v>
       </c>
@@ -13977,7 +13977,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="527" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C527" s="7">
         <v>454</v>
       </c>
@@ -14015,7 +14015,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="528" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C528" s="7">
         <v>455</v>
       </c>
@@ -14053,7 +14053,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="529" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="529" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C529" s="7">
         <v>456</v>
       </c>
@@ -14091,7 +14091,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="530" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="530" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C530" s="7">
         <v>457</v>
       </c>
@@ -14129,7 +14129,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="531" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="531" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C531" s="7">
         <v>458</v>
       </c>
@@ -14167,7 +14167,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="532" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="532" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C532" s="7">
         <v>460</v>
       </c>
@@ -14205,7 +14205,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="533" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="533" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C533" s="7">
         <v>461</v>
       </c>
@@ -14243,7 +14243,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="534" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="534" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C534" s="7">
         <v>462</v>
       </c>
@@ -14281,7 +14281,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="535" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="535" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C535" s="7">
         <v>463</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="536" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="536" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C536" s="7">
         <v>464</v>
       </c>
@@ -14357,7 +14357,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="537" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="537" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C537" s="7">
         <v>465</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="538" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="538" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C538" s="7">
         <v>466</v>
       </c>
@@ -14433,7 +14433,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="539" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="539" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C539" s="7">
         <v>467</v>
       </c>
@@ -14471,7 +14471,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="540" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="540" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C540" s="7">
         <v>468</v>
       </c>
@@ -14509,7 +14509,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="541" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="541" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C541" s="7">
         <v>469</v>
       </c>
@@ -14547,7 +14547,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="542" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="542" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C542" s="7">
         <v>470</v>
       </c>
@@ -14585,7 +14585,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="543" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="543" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C543" s="7">
         <v>471</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="544" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="544" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C544" s="7">
         <v>472</v>
       </c>
@@ -14661,7 +14661,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="545" spans="3:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="3:22" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C545" s="15">
         <v>473</v>
       </c>
@@ -14699,7 +14699,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="546" spans="3:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="3:22" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C546" s="19"/>
       <c r="D546" s="20"/>
       <c r="E546" s="20"/>
@@ -14723,7 +14723,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="547" spans="3:22" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="547" spans="3:22" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C547" s="4" t="s">
         <v>0</v>
       </c>
@@ -14761,7 +14761,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="548" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="548" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C548" s="7">
         <v>474</v>
       </c>
@@ -14799,7 +14799,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="549" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="549" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C549" s="7">
         <v>475</v>
       </c>
@@ -14837,7 +14837,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="550" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="550" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C550" s="7">
         <v>476</v>
       </c>
@@ -14875,7 +14875,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="551" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="551" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C551" s="7">
         <v>477</v>
       </c>
@@ -14913,7 +14913,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="552" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="552" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C552" s="7">
         <v>478</v>
       </c>
@@ -14951,7 +14951,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="553" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="553" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C553" s="7">
         <v>479</v>
       </c>
@@ -14989,7 +14989,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="554" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="554" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C554" s="7">
         <v>480</v>
       </c>
@@ -15027,7 +15027,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="555" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="555" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C555" s="7">
         <v>481</v>
       </c>
@@ -15065,7 +15065,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="556" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="556" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C556" s="7">
         <v>482</v>
       </c>
@@ -15088,7 +15088,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="557" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="557" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C557" s="7">
         <v>483</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="558" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="558" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C558" s="7">
         <v>484</v>
       </c>
@@ -15134,7 +15134,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="559" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="559" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C559" s="7">
         <v>485</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="560" spans="3:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="560" spans="3:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C560" s="7">
         <v>486</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="561" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="561" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C561" s="7">
         <v>488</v>
       </c>
@@ -15203,7 +15203,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="562" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="562" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C562" s="7">
         <v>489</v>
       </c>
@@ -15226,7 +15226,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="563" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="563" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C563" s="7">
         <v>490</v>
       </c>
@@ -15249,7 +15249,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="564" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="564" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C564" s="7">
         <v>493</v>
       </c>
@@ -15272,7 +15272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="565" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="565" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C565" s="11">
         <v>494</v>
       </c>
@@ -15295,7 +15295,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="566" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="566" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C566" s="11">
         <v>495</v>
       </c>
@@ -15318,7 +15318,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="567" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="567" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C567" s="11">
         <v>496</v>
       </c>
@@ -15341,7 +15341,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="568" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="568" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C568" s="11">
         <v>497</v>
       </c>
@@ -15364,7 +15364,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="569" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="569" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C569" s="11">
         <v>498</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="570" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="570" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C570" s="11">
         <v>499</v>
       </c>
@@ -15410,7 +15410,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="571" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="571" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C571" s="11">
         <v>500</v>
       </c>
@@ -15433,7 +15433,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="572" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="572" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C572" s="11">
         <v>501</v>
       </c>
@@ -15456,7 +15456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="573" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="3:9" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C573" s="15">
         <v>502</v>
       </c>
@@ -15479,7 +15479,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="574" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="574" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C574" s="19"/>
       <c r="D574" s="20"/>
       <c r="E574" s="20"/>
@@ -15488,7 +15488,7 @@
       <c r="H574" s="19"/>
       <c r="I574" s="3"/>
     </row>
-    <row r="575" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="575" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C575" s="19"/>
       <c r="D575" s="20"/>
       <c r="E575" s="20"/>
@@ -15497,7 +15497,7 @@
       <c r="H575" s="19"/>
       <c r="I575" s="3"/>
     </row>
-    <row r="576" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="576" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C576" s="19"/>
       <c r="D576" s="20"/>
       <c r="E576" s="20"/>
@@ -15506,7 +15506,7 @@
       <c r="H576" s="19"/>
       <c r="I576" s="3"/>
     </row>
-    <row r="577" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C577" s="19"/>
       <c r="D577" s="20"/>
       <c r="E577" s="20"/>
@@ -15515,7 +15515,7 @@
       <c r="H577" s="19"/>
       <c r="I577" s="3"/>
     </row>
-    <row r="578" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C578" s="19"/>
       <c r="D578" s="20"/>
       <c r="E578" s="20"/>
@@ -15524,7 +15524,7 @@
       <c r="H578" s="19"/>
       <c r="I578" s="3"/>
     </row>
-    <row r="579" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C579" s="19"/>
       <c r="D579" s="20"/>
       <c r="E579" s="20"/>
@@ -15533,7 +15533,7 @@
       <c r="H579" s="19"/>
       <c r="I579" s="3"/>
     </row>
-    <row r="580" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C580" s="19"/>
       <c r="D580" s="20"/>
       <c r="E580" s="20"/>
@@ -15542,151 +15542,151 @@
       <c r="H580" s="19"/>
       <c r="I580" s="3"/>
     </row>
-    <row r="581" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A581" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B581" s="2"/>
       <c r="C581" s="2"/>
       <c r="D581" s="2"/>
-      <c r="E581" s="64" t="s">
+      <c r="E581" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F581" s="65"/>
-      <c r="G581" s="66"/>
-      <c r="H581" s="67" t="s">
+      <c r="F581" s="67"/>
+      <c r="G581" s="68"/>
+      <c r="H581" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I581" s="68"/>
-      <c r="J581" s="71"/>
-      <c r="K581" s="72"/>
-    </row>
-    <row r="582" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A582" s="75" t="s">
+      <c r="I581" s="70"/>
+      <c r="J581" s="73"/>
+      <c r="K581" s="74"/>
+    </row>
+    <row r="582" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A582" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B582" s="76"/>
-      <c r="C582" s="76"/>
-      <c r="D582" s="77"/>
-      <c r="E582" s="78">
+      <c r="B582" s="78"/>
+      <c r="C582" s="78"/>
+      <c r="D582" s="79"/>
+      <c r="E582" s="80">
         <v>140</v>
       </c>
-      <c r="F582" s="79"/>
-      <c r="G582" s="80"/>
-      <c r="H582" s="69"/>
-      <c r="I582" s="70"/>
-      <c r="J582" s="73"/>
-      <c r="K582" s="74"/>
-    </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A583" s="53"/>
-      <c r="B583" s="53"/>
-      <c r="C583" s="53"/>
-      <c r="D583" s="53"/>
-      <c r="E583" s="53"/>
-      <c r="F583" s="53"/>
-      <c r="G583" s="53"/>
-      <c r="H583" s="53"/>
-      <c r="I583" s="53"/>
-      <c r="J583" s="53"/>
-      <c r="K583" s="53"/>
-    </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A584" s="53"/>
-      <c r="B584" s="53"/>
-      <c r="C584" s="53"/>
-      <c r="D584" s="53"/>
-      <c r="E584" s="53"/>
-      <c r="F584" s="53"/>
-      <c r="G584" s="53"/>
-      <c r="H584" s="53"/>
-      <c r="I584" s="53"/>
-      <c r="J584" s="53"/>
-      <c r="K584" s="53"/>
-    </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A585" s="54" t="s">
+      <c r="F582" s="81"/>
+      <c r="G582" s="82"/>
+      <c r="H582" s="71"/>
+      <c r="I582" s="72"/>
+      <c r="J582" s="75"/>
+      <c r="K582" s="76"/>
+    </row>
+    <row r="583" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A583" s="65"/>
+      <c r="B583" s="65"/>
+      <c r="C583" s="65"/>
+      <c r="D583" s="65"/>
+      <c r="E583" s="65"/>
+      <c r="F583" s="65"/>
+      <c r="G583" s="65"/>
+      <c r="H583" s="65"/>
+      <c r="I583" s="65"/>
+      <c r="J583" s="65"/>
+      <c r="K583" s="65"/>
+    </row>
+    <row r="584" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A584" s="65"/>
+      <c r="B584" s="65"/>
+      <c r="C584" s="65"/>
+      <c r="D584" s="65"/>
+      <c r="E584" s="65"/>
+      <c r="F584" s="65"/>
+      <c r="G584" s="65"/>
+      <c r="H584" s="65"/>
+      <c r="I584" s="65"/>
+      <c r="J584" s="65"/>
+      <c r="K584" s="65"/>
+    </row>
+    <row r="585" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A585" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B585" s="54"/>
-      <c r="C585" s="54"/>
-      <c r="D585" s="54"/>
-      <c r="E585" s="54"/>
-      <c r="F585" s="54"/>
-      <c r="G585" s="54"/>
-      <c r="H585" s="54"/>
-      <c r="I585" s="54"/>
-      <c r="J585" s="54"/>
-      <c r="K585" s="54"/>
-    </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A586" s="54"/>
-      <c r="B586" s="54"/>
-      <c r="C586" s="54"/>
-      <c r="D586" s="54"/>
-      <c r="E586" s="54"/>
-      <c r="F586" s="54"/>
-      <c r="G586" s="54"/>
-      <c r="H586" s="54"/>
-      <c r="I586" s="54"/>
-      <c r="J586" s="54"/>
-      <c r="K586" s="54"/>
-    </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A587" s="54"/>
-      <c r="B587" s="54"/>
-      <c r="C587" s="54"/>
-      <c r="D587" s="54"/>
-      <c r="E587" s="54"/>
-      <c r="F587" s="54"/>
-      <c r="G587" s="54"/>
-      <c r="H587" s="54"/>
-      <c r="I587" s="54"/>
-      <c r="J587" s="54"/>
-      <c r="K587" s="54"/>
-    </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A588" s="54"/>
-      <c r="B588" s="54"/>
-      <c r="C588" s="54"/>
-      <c r="D588" s="54"/>
-      <c r="E588" s="54"/>
-      <c r="F588" s="54"/>
-      <c r="G588" s="54"/>
-      <c r="H588" s="54"/>
-      <c r="I588" s="54"/>
-      <c r="J588" s="54"/>
-      <c r="K588" s="54"/>
-    </row>
-    <row r="589" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C590" s="55"/>
-      <c r="D590" s="56"/>
-      <c r="E590" s="56"/>
-      <c r="F590" s="56"/>
-      <c r="G590" s="56"/>
-      <c r="H590" s="56"/>
-      <c r="I590" s="57"/>
-    </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C591" s="58"/>
-      <c r="D591" s="59"/>
-      <c r="E591" s="59"/>
-      <c r="F591" s="59"/>
-      <c r="G591" s="59"/>
-      <c r="H591" s="59"/>
-      <c r="I591" s="60"/>
-    </row>
-    <row r="592" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C592" s="61"/>
-      <c r="D592" s="62"/>
-      <c r="E592" s="62"/>
-      <c r="F592" s="62"/>
-      <c r="G592" s="62"/>
-      <c r="H592" s="62"/>
-      <c r="I592" s="63"/>
-    </row>
-    <row r="593" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B585" s="55"/>
+      <c r="C585" s="55"/>
+      <c r="D585" s="55"/>
+      <c r="E585" s="55"/>
+      <c r="F585" s="55"/>
+      <c r="G585" s="55"/>
+      <c r="H585" s="55"/>
+      <c r="I585" s="55"/>
+      <c r="J585" s="55"/>
+      <c r="K585" s="55"/>
+    </row>
+    <row r="586" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A586" s="55"/>
+      <c r="B586" s="55"/>
+      <c r="C586" s="55"/>
+      <c r="D586" s="55"/>
+      <c r="E586" s="55"/>
+      <c r="F586" s="55"/>
+      <c r="G586" s="55"/>
+      <c r="H586" s="55"/>
+      <c r="I586" s="55"/>
+      <c r="J586" s="55"/>
+      <c r="K586" s="55"/>
+    </row>
+    <row r="587" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A587" s="55"/>
+      <c r="B587" s="55"/>
+      <c r="C587" s="55"/>
+      <c r="D587" s="55"/>
+      <c r="E587" s="55"/>
+      <c r="F587" s="55"/>
+      <c r="G587" s="55"/>
+      <c r="H587" s="55"/>
+      <c r="I587" s="55"/>
+      <c r="J587" s="55"/>
+      <c r="K587" s="55"/>
+    </row>
+    <row r="588" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A588" s="55"/>
+      <c r="B588" s="55"/>
+      <c r="C588" s="55"/>
+      <c r="D588" s="55"/>
+      <c r="E588" s="55"/>
+      <c r="F588" s="55"/>
+      <c r="G588" s="55"/>
+      <c r="H588" s="55"/>
+      <c r="I588" s="55"/>
+      <c r="J588" s="55"/>
+      <c r="K588" s="55"/>
+    </row>
+    <row r="589" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="590" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C590" s="56"/>
+      <c r="D590" s="57"/>
+      <c r="E590" s="57"/>
+      <c r="F590" s="57"/>
+      <c r="G590" s="57"/>
+      <c r="H590" s="57"/>
+      <c r="I590" s="58"/>
+    </row>
+    <row r="591" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C591" s="59"/>
+      <c r="D591" s="60"/>
+      <c r="E591" s="60"/>
+      <c r="F591" s="60"/>
+      <c r="G591" s="60"/>
+      <c r="H591" s="60"/>
+      <c r="I591" s="61"/>
+    </row>
+    <row r="592" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C592" s="62"/>
+      <c r="D592" s="63"/>
+      <c r="E592" s="63"/>
+      <c r="F592" s="63"/>
+      <c r="G592" s="63"/>
+      <c r="H592" s="63"/>
+      <c r="I592" s="64"/>
+    </row>
+    <row r="593" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C593" s="19"/>
       <c r="D593" s="20"/>
       <c r="E593" s="20"/>
@@ -15695,7 +15695,7 @@
       <c r="H593" s="19"/>
       <c r="I593" s="3"/>
     </row>
-    <row r="594" spans="3:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="594" spans="3:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C594" s="38" t="s">
         <v>0</v>
       </c>
@@ -15718,7 +15718,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="595" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="595" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C595" s="9">
         <v>503</v>
       </c>
@@ -15741,7 +15741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="596" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="596" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C596" s="9">
         <v>504</v>
       </c>
@@ -15764,7 +15764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="597" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="597" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C597" s="9">
         <v>505</v>
       </c>
@@ -15787,7 +15787,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="598" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="598" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C598" s="9">
         <v>506</v>
       </c>
@@ -15810,7 +15810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="599" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="599" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C599" s="9">
         <v>507</v>
       </c>
@@ -15833,7 +15833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="600" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="600" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C600" s="9">
         <v>508</v>
       </c>
@@ -15856,7 +15856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="601" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="601" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C601" s="9">
         <v>509</v>
       </c>
@@ -15879,7 +15879,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="602" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="602" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C602" s="9">
         <v>510</v>
       </c>
@@ -15902,7 +15902,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="603" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="603" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C603" s="9">
         <v>511</v>
       </c>
@@ -15925,7 +15925,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="604" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="604" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C604" s="9">
         <v>512</v>
       </c>
@@ -15948,7 +15948,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="605" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="605" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C605" s="9">
         <v>513</v>
       </c>
@@ -15971,7 +15971,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="606" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="606" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C606" s="9">
         <v>514</v>
       </c>
@@ -15994,7 +15994,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="607" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="607" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C607" s="9">
         <v>515</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="608" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="608" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C608" s="9">
         <v>516</v>
       </c>
@@ -16040,7 +16040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="609" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="609" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C609" s="9">
         <v>517</v>
       </c>
@@ -16063,7 +16063,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="610" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="610" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C610" s="9">
         <v>518</v>
       </c>
@@ -16086,7 +16086,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="611" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="611" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C611" s="9">
         <v>519</v>
       </c>
@@ -16109,7 +16109,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="612" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="612" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C612" s="9">
         <v>520</v>
       </c>
@@ -16132,7 +16132,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="613" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="613" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C613" s="9">
         <v>521</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="614" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="614" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C614" s="9">
         <v>522</v>
       </c>
@@ -16178,7 +16178,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="615" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="615" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C615" s="9">
         <v>523</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="616" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="616" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C616" s="9">
         <v>524</v>
       </c>
@@ -16224,7 +16224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="617" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="617" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C617" s="9">
         <v>525</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="618" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="618" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C618" s="9">
         <v>526</v>
       </c>
@@ -16270,7 +16270,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="619" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="619" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C619" s="9">
         <v>527</v>
       </c>
@@ -16293,7 +16293,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="620" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="620" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C620" s="9">
         <v>528</v>
       </c>
@@ -16316,7 +16316,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="621" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="621" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C621" s="9">
         <v>529</v>
       </c>
@@ -16339,7 +16339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="622" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="622" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C622" s="9">
         <v>530</v>
       </c>
@@ -16362,7 +16362,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="623" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="623" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C623" s="9">
         <v>531</v>
       </c>
@@ -16385,7 +16385,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="624" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="624" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C624" s="9">
         <v>532</v>
       </c>
@@ -16408,7 +16408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="625" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="625" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C625" s="9">
         <v>533</v>
       </c>
@@ -16431,7 +16431,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="626" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="626" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C626" s="9">
         <v>534</v>
       </c>
@@ -16454,7 +16454,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="627" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="627" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C627" s="9">
         <v>535</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="628" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="628" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C628" s="9">
         <v>536</v>
       </c>
@@ -16500,7 +16500,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="629" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="629" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C629" s="9">
         <v>537</v>
       </c>
@@ -16523,7 +16523,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="630" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="630" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C630" s="9">
         <v>538</v>
       </c>
@@ -16546,7 +16546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="631" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="631" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C631" s="9">
         <v>539</v>
       </c>
@@ -16569,7 +16569,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="632" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="632" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C632" s="9">
         <v>540</v>
       </c>
@@ -16592,7 +16592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="633" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="633" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C633" s="9">
         <v>541</v>
       </c>
@@ -16615,7 +16615,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="634" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="634" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C634" s="9">
         <v>542</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="635" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="635" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C635" s="9">
         <v>543</v>
       </c>
@@ -16661,7 +16661,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="636" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="636" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C636" s="9">
         <v>544</v>
       </c>
@@ -16684,7 +16684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="637" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="637" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C637" s="9">
         <v>545</v>
       </c>
@@ -16707,7 +16707,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="638" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="638" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C638" s="9">
         <v>546</v>
       </c>
@@ -16730,7 +16730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="639" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="639" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C639" s="9">
         <v>547</v>
       </c>
@@ -16753,7 +16753,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="640" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="640" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C640" s="9">
         <v>548</v>
       </c>
@@ -16776,7 +16776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="641" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C641" s="9">
         <v>549</v>
       </c>
@@ -16799,7 +16799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="642" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C642" s="9">
         <v>550</v>
       </c>
@@ -16822,7 +16822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="643" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C643" s="9">
         <v>551</v>
       </c>
@@ -16845,7 +16845,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="644" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C644" s="9">
         <v>552</v>
       </c>
@@ -16868,7 +16868,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="645" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C645" s="9">
         <v>553</v>
       </c>
@@ -16891,7 +16891,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="646" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C646" s="9">
         <v>554</v>
       </c>
@@ -16914,7 +16914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="647" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C647" s="19"/>
       <c r="D647" s="20"/>
       <c r="E647" s="20"/>
@@ -16923,7 +16923,7 @@
       <c r="H647" s="19"/>
       <c r="I647" s="3"/>
     </row>
-    <row r="648" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C648" s="19"/>
       <c r="D648" s="20"/>
       <c r="E648" s="20"/>
@@ -16932,7 +16932,7 @@
       <c r="H648" s="19"/>
       <c r="I648" s="3"/>
     </row>
-    <row r="649" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C649" s="19"/>
       <c r="D649" s="20"/>
       <c r="E649" s="20"/>
@@ -16941,7 +16941,7 @@
       <c r="H649" s="19"/>
       <c r="I649" s="3"/>
     </row>
-    <row r="650" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C650" s="19"/>
       <c r="D650" s="20"/>
       <c r="E650" s="20"/>
@@ -16950,7 +16950,7 @@
       <c r="H650" s="19"/>
       <c r="I650" s="3"/>
     </row>
-    <row r="651" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C651" s="19"/>
       <c r="D651" s="20"/>
       <c r="E651" s="20"/>
@@ -16959,7 +16959,7 @@
       <c r="H651" s="19"/>
       <c r="I651" s="3"/>
     </row>
-    <row r="652" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C652" s="19"/>
       <c r="D652" s="20"/>
       <c r="E652" s="20"/>
@@ -16968,7 +16968,7 @@
       <c r="H652" s="19"/>
       <c r="I652" s="3"/>
     </row>
-    <row r="653" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C653" s="19"/>
       <c r="D653" s="20"/>
       <c r="E653" s="20"/>
@@ -16977,7 +16977,7 @@
       <c r="H653" s="19"/>
       <c r="I653" s="3"/>
     </row>
-    <row r="654" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C654" s="19"/>
       <c r="D654" s="20"/>
       <c r="E654" s="20"/>
@@ -16986,43 +16986,43 @@
       <c r="H654" s="19"/>
       <c r="I654" s="3"/>
     </row>
-    <row r="655" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A655" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B655" s="2"/>
       <c r="C655" s="2"/>
       <c r="D655" s="2"/>
-      <c r="E655" s="64" t="s">
+      <c r="E655" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F655" s="65"/>
-      <c r="G655" s="66"/>
-      <c r="H655" s="67" t="s">
+      <c r="F655" s="67"/>
+      <c r="G655" s="68"/>
+      <c r="H655" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I655" s="68"/>
-      <c r="J655" s="71"/>
-      <c r="K655" s="72"/>
-    </row>
-    <row r="656" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A656" s="75" t="s">
+      <c r="I655" s="70"/>
+      <c r="J655" s="73"/>
+      <c r="K655" s="74"/>
+    </row>
+    <row r="656" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A656" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B656" s="76"/>
-      <c r="C656" s="76"/>
-      <c r="D656" s="77"/>
-      <c r="E656" s="78">
+      <c r="B656" s="78"/>
+      <c r="C656" s="78"/>
+      <c r="D656" s="79"/>
+      <c r="E656" s="80">
         <v>140</v>
       </c>
-      <c r="F656" s="79"/>
-      <c r="G656" s="80"/>
-      <c r="H656" s="69"/>
-      <c r="I656" s="70"/>
-      <c r="J656" s="73"/>
-      <c r="K656" s="74"/>
-    </row>
-    <row r="657" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="F656" s="81"/>
+      <c r="G656" s="82"/>
+      <c r="H656" s="71"/>
+      <c r="I656" s="72"/>
+      <c r="J656" s="75"/>
+      <c r="K656" s="76"/>
+    </row>
+    <row r="657" spans="3:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="C657" s="19"/>
       <c r="D657" s="20"/>
       <c r="E657" s="20"/>
@@ -17033,22 +17033,47 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="A293:K296"/>
-    <mergeCell ref="C298:I300"/>
-    <mergeCell ref="A363:K364"/>
-    <mergeCell ref="A365:K368"/>
-    <mergeCell ref="C370:I372"/>
-    <mergeCell ref="E360:G360"/>
-    <mergeCell ref="H360:I361"/>
-    <mergeCell ref="J360:K361"/>
-    <mergeCell ref="A361:D361"/>
-    <mergeCell ref="E361:G361"/>
-    <mergeCell ref="E289:G289"/>
-    <mergeCell ref="H289:I290"/>
-    <mergeCell ref="J289:K290"/>
-    <mergeCell ref="A290:D290"/>
-    <mergeCell ref="A291:K292"/>
-    <mergeCell ref="E290:G290"/>
+    <mergeCell ref="A583:K584"/>
+    <mergeCell ref="A585:K588"/>
+    <mergeCell ref="C590:I592"/>
+    <mergeCell ref="E655:G655"/>
+    <mergeCell ref="H655:I656"/>
+    <mergeCell ref="J655:K656"/>
+    <mergeCell ref="A656:D656"/>
+    <mergeCell ref="E656:G656"/>
+    <mergeCell ref="E581:G581"/>
+    <mergeCell ref="H581:I582"/>
+    <mergeCell ref="J581:K582"/>
+    <mergeCell ref="A582:D582"/>
+    <mergeCell ref="E582:G582"/>
+    <mergeCell ref="A510:K511"/>
+    <mergeCell ref="A512:K515"/>
+    <mergeCell ref="C517:I519"/>
+    <mergeCell ref="E435:G435"/>
+    <mergeCell ref="H435:I436"/>
+    <mergeCell ref="J435:K436"/>
+    <mergeCell ref="A436:D436"/>
+    <mergeCell ref="E436:G436"/>
+    <mergeCell ref="A438:K439"/>
+    <mergeCell ref="A440:K443"/>
+    <mergeCell ref="C445:I447"/>
+    <mergeCell ref="E509:G509"/>
+    <mergeCell ref="E508:G508"/>
+    <mergeCell ref="H508:I509"/>
+    <mergeCell ref="J508:K509"/>
+    <mergeCell ref="A509:D509"/>
+    <mergeCell ref="A219:K222"/>
+    <mergeCell ref="B62:H63"/>
+    <mergeCell ref="A72:K73"/>
+    <mergeCell ref="A74:K77"/>
+    <mergeCell ref="C79:I81"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="H215:I216"/>
+    <mergeCell ref="J215:K216"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="E216:G216"/>
+    <mergeCell ref="A217:K218"/>
     <mergeCell ref="C224:I226"/>
     <mergeCell ref="C8:I10"/>
     <mergeCell ref="A3:K6"/>
@@ -17065,47 +17090,22 @@
     <mergeCell ref="A147:K150"/>
     <mergeCell ref="C152:I154"/>
     <mergeCell ref="E215:G215"/>
-    <mergeCell ref="A219:K222"/>
-    <mergeCell ref="B62:H63"/>
-    <mergeCell ref="A72:K73"/>
-    <mergeCell ref="A74:K77"/>
-    <mergeCell ref="C79:I81"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="H215:I216"/>
-    <mergeCell ref="J215:K216"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="E216:G216"/>
-    <mergeCell ref="A217:K218"/>
-    <mergeCell ref="A510:K511"/>
-    <mergeCell ref="A512:K515"/>
-    <mergeCell ref="C517:I519"/>
-    <mergeCell ref="E435:G435"/>
-    <mergeCell ref="H435:I436"/>
-    <mergeCell ref="J435:K436"/>
-    <mergeCell ref="A436:D436"/>
-    <mergeCell ref="E436:G436"/>
-    <mergeCell ref="A438:K439"/>
-    <mergeCell ref="A440:K443"/>
-    <mergeCell ref="C445:I447"/>
-    <mergeCell ref="E509:G509"/>
-    <mergeCell ref="E508:G508"/>
-    <mergeCell ref="H508:I509"/>
-    <mergeCell ref="J508:K509"/>
-    <mergeCell ref="A509:D509"/>
-    <mergeCell ref="E581:G581"/>
-    <mergeCell ref="H581:I582"/>
-    <mergeCell ref="J581:K582"/>
-    <mergeCell ref="A582:D582"/>
-    <mergeCell ref="E582:G582"/>
-    <mergeCell ref="A583:K584"/>
-    <mergeCell ref="A585:K588"/>
-    <mergeCell ref="C590:I592"/>
-    <mergeCell ref="E655:G655"/>
-    <mergeCell ref="H655:I656"/>
-    <mergeCell ref="J655:K656"/>
-    <mergeCell ref="A656:D656"/>
-    <mergeCell ref="E656:G656"/>
+    <mergeCell ref="E289:G289"/>
+    <mergeCell ref="H289:I290"/>
+    <mergeCell ref="J289:K290"/>
+    <mergeCell ref="A290:D290"/>
+    <mergeCell ref="A291:K292"/>
+    <mergeCell ref="E290:G290"/>
+    <mergeCell ref="A293:K296"/>
+    <mergeCell ref="C298:I300"/>
+    <mergeCell ref="A363:K364"/>
+    <mergeCell ref="A365:K368"/>
+    <mergeCell ref="C370:I372"/>
+    <mergeCell ref="E360:G360"/>
+    <mergeCell ref="H360:I361"/>
+    <mergeCell ref="J360:K361"/>
+    <mergeCell ref="A361:D361"/>
+    <mergeCell ref="E361:G361"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="60" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -17116,38 +17116,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:U48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="82" t="s">
+    <row r="2" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="O2" s="82" t="s">
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="O2" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="82"/>
-      <c r="Q2" s="82"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="82"/>
-    </row>
-    <row r="3" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="84"/>
+      <c r="S2" s="84"/>
+    </row>
+    <row r="3" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="21" t="s">
         <v>22</v>
       </c>
@@ -17182,7 +17182,7 @@
         <v>0.56108916851037305</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="23" t="s">
         <v>27</v>
       </c>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>27</v>
       </c>
@@ -17246,7 +17246,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B6" s="23" t="s">
         <v>27</v>
       </c>
@@ -17281,7 +17281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="23" t="s">
         <v>27</v>
       </c>
@@ -17327,7 +17327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" s="23" t="s">
         <v>27</v>
       </c>
@@ -17366,7 +17366,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="31" t="s">
         <v>36</v>
       </c>
@@ -17400,7 +17400,7 @@
         <v>493.45548013813271</v>
       </c>
     </row>
-    <row r="10" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="31" t="s">
         <v>24</v>
       </c>
@@ -17434,7 +17434,7 @@
         <v>493.45548013813271</v>
       </c>
     </row>
-    <row r="11" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="31" t="s">
         <v>25</v>
       </c>
@@ -17468,7 +17468,7 @@
         <v>465.73767521372019</v>
       </c>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" s="23" t="s">
         <v>27</v>
       </c>
@@ -17500,7 +17500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="31" t="s">
         <v>36</v>
       </c>
@@ -17534,7 +17534,7 @@
         <v>233.35137429177905</v>
       </c>
     </row>
-    <row r="14" spans="2:21" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="31" t="s">
         <v>24</v>
       </c>
@@ -17568,7 +17568,7 @@
         <v>233.35137429177905</v>
       </c>
     </row>
-    <row r="15" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="31" t="s">
         <v>15</v>
       </c>
@@ -17602,7 +17602,7 @@
         <v>466.49514559120922</v>
       </c>
     </row>
-    <row r="16" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="31" t="s">
         <v>25</v>
       </c>
@@ -17636,7 +17636,7 @@
         <v>232.47046429721775</v>
       </c>
     </row>
-    <row r="17" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="31" t="s">
         <v>15</v>
       </c>
@@ -17670,7 +17670,7 @@
         <v>232.53779499743899</v>
       </c>
     </row>
-    <row r="18" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="31" t="s">
         <v>17</v>
       </c>
@@ -17704,7 +17704,7 @@
         <v>462.92661847948324</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="23" t="s">
         <v>27</v>
       </c>
@@ -17736,7 +17736,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="23" t="s">
         <v>27</v>
       </c>
@@ -17768,7 +17768,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21" s="23" t="s">
         <v>27</v>
       </c>
@@ -17800,7 +17800,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="31" t="s">
         <v>17</v>
       </c>
@@ -17834,7 +17834,7 @@
         <v>228.13885591631768</v>
       </c>
     </row>
-    <row r="23" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B23" s="31" t="s">
         <v>53</v>
       </c>
@@ -17869,7 +17869,7 @@
         <v>474.69826923483089</v>
       </c>
     </row>
-    <row r="24" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:19" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B24" s="31" t="s">
         <v>53</v>
       </c>
@@ -17903,7 +17903,7 @@
         <v>233.81146740995754</v>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C25">
         <f>C9+C10+C11+C13+C14+C15+C16+C17+C18+C22+C23+C24</f>
         <v>7575.32</v>
@@ -17930,7 +17930,7 @@
         <v>5090.43</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="F26" s="30">
         <f>F25*10%</f>
         <v>462.76600000000002</v>
@@ -17939,7 +17939,7 @@
         <v>462.76600000000002</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="F27" s="30">
         <f>F25*0.1</f>
         <v>462.76600000000002</v>
@@ -17948,7 +17948,7 @@
         <v>462.76600000000002</v>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="F28" s="30">
         <f>F25+F27</f>
         <v>5090.4259999999995</v>
@@ -17972,7 +17972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="O29" t="s">
         <v>27</v>
       </c>
@@ -17989,7 +17989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="O30" t="s">
         <v>27</v>
       </c>
@@ -18006,7 +18006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="O31" t="s">
         <v>27</v>
       </c>
@@ -18023,7 +18023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="O32" t="s">
         <v>27</v>
       </c>
@@ -18040,7 +18040,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:19" x14ac:dyDescent="0.3">
       <c r="O33" t="s">
         <v>27</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:19" x14ac:dyDescent="0.3">
       <c r="O34" t="s">
         <v>27</v>
       </c>
@@ -18074,7 +18074,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:19" x14ac:dyDescent="0.3">
       <c r="O35" t="s">
         <v>27</v>
       </c>
@@ -18091,7 +18091,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="10:19" x14ac:dyDescent="0.3">
       <c r="O36" t="s">
         <v>27</v>
       </c>
@@ -18108,7 +18108,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="37" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J37" t="s">
         <v>65</v>
       </c>
@@ -18132,7 +18132,7 @@
         <v>232.4704642972178</v>
       </c>
     </row>
-    <row r="38" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J38" t="s">
         <v>66</v>
       </c>
@@ -18156,7 +18156,7 @@
         <v>465.73767521372031</v>
       </c>
     </row>
-    <row r="39" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J39" t="s">
         <v>59</v>
       </c>
@@ -18179,7 +18179,7 @@
         <v>233.35137429177908</v>
       </c>
     </row>
-    <row r="40" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J40" t="s">
         <v>60</v>
       </c>
@@ -18203,7 +18203,7 @@
         <v>493.45548013813283</v>
       </c>
     </row>
-    <row r="41" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J41" t="s">
         <v>57</v>
       </c>
@@ -18227,7 +18227,7 @@
         <v>228.13885591631774</v>
       </c>
     </row>
-    <row r="42" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J42" t="s">
         <v>58</v>
       </c>
@@ -18251,7 +18251,7 @@
         <v>462.92661847948335</v>
       </c>
     </row>
-    <row r="43" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J43" t="s">
         <v>67</v>
       </c>
@@ -18275,7 +18275,7 @@
         <v>233.8114674099576</v>
       </c>
     </row>
-    <row r="44" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J44" t="s">
         <v>68</v>
       </c>
@@ -18299,7 +18299,7 @@
         <v>474.698269234831</v>
       </c>
     </row>
-    <row r="45" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J45" t="s">
         <v>61</v>
       </c>
@@ -18323,7 +18323,7 @@
         <v>233.35137429177908</v>
       </c>
     </row>
-    <row r="46" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J46" t="s">
         <v>62</v>
       </c>
@@ -18347,7 +18347,7 @@
         <v>493.45548013813283</v>
       </c>
     </row>
-    <row r="47" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J47" t="s">
         <v>63</v>
       </c>
@@ -18371,7 +18371,7 @@
         <v>232.53779499743905</v>
       </c>
     </row>
-    <row r="48" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J48" t="s">
         <v>64</v>
       </c>
@@ -18396,7 +18396,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O28:S48">
+  <sortState ref="O28:S48">
     <sortCondition ref="O36"/>
   </sortState>
   <mergeCells count="2">
@@ -18411,31 +18411,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:L59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="82" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="21" t="s">
         <v>22</v>
       </c>
@@ -18452,7 +18452,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="23" t="s">
         <v>27</v>
       </c>
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>27</v>
       </c>
@@ -18486,7 +18486,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="23" t="s">
         <v>27</v>
       </c>
@@ -18503,7 +18503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="23" t="s">
         <v>27</v>
       </c>
@@ -18520,7 +18520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="23" t="s">
         <v>27</v>
       </c>
@@ -18537,7 +18537,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="23" t="s">
         <v>36</v>
       </c>
@@ -18554,7 +18554,7 @@
         <v>493.45548013813271</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="23" t="s">
         <v>24</v>
       </c>
@@ -18571,7 +18571,7 @@
         <v>493.45548013813271</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="23" t="s">
         <v>25</v>
       </c>
@@ -18588,7 +18588,7 @@
         <v>465.73767521372019</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="23" t="s">
         <v>27</v>
       </c>
@@ -18605,7 +18605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="23" t="s">
         <v>36</v>
       </c>
@@ -18622,7 +18622,7 @@
         <v>233.35137429177905</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="23" t="s">
         <v>24</v>
       </c>
@@ -18639,7 +18639,7 @@
         <v>233.35137429177905</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="23" t="s">
         <v>15</v>
       </c>
@@ -18656,7 +18656,7 @@
         <v>466.49514559120922</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="23" t="s">
         <v>25</v>
       </c>
@@ -18673,7 +18673,7 @@
         <v>232.47046429721775</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="23" t="s">
         <v>15</v>
       </c>
@@ -18690,7 +18690,7 @@
         <v>232.53779499743899</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="23" t="s">
         <v>17</v>
       </c>
@@ -18707,7 +18707,7 @@
         <v>462.92661847948324</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="23" t="s">
         <v>27</v>
       </c>
@@ -18724,7 +18724,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="23" t="s">
         <v>27</v>
       </c>
@@ -18741,7 +18741,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="23" t="s">
         <v>27</v>
       </c>
@@ -18758,7 +18758,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="23" t="s">
         <v>17</v>
       </c>
@@ -18775,7 +18775,7 @@
         <v>228.13885591631768</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="23" t="s">
         <v>53</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>474.69826923483089</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="23" t="s">
         <v>53</v>
       </c>
@@ -18815,7 +18815,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="23" t="s">
         <v>72</v>
       </c>
@@ -18833,7 +18833,7 @@
         <v>456.74902673418404</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="23" t="s">
         <v>72</v>
       </c>
@@ -18851,7 +18851,7 @@
         <v>228.63261438460682</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="23" t="s">
         <v>89</v>
       </c>
@@ -18869,7 +18869,7 @@
         <v>452.66990847911364</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="23" t="s">
         <v>89</v>
       </c>
@@ -18887,7 +18887,7 @@
         <v>223.97557428597071</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="23" t="s">
         <v>90</v>
       </c>
@@ -18905,7 +18905,7 @@
         <v>448.83766945818786</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="23" t="s">
         <v>90</v>
       </c>
@@ -18923,7 +18923,7 @@
         <v>223.29104550038804</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="23" t="s">
         <v>91</v>
       </c>
@@ -18941,7 +18941,7 @@
         <v>453.35443726469634</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="23" t="s">
         <v>91</v>
       </c>
@@ -18959,7 +18959,7 @@
         <v>224.43566740414923</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="23" t="s">
         <v>92</v>
       </c>
@@ -18977,7 +18977,7 @@
         <v>449.28654079299611</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="23" t="s">
         <v>92</v>
       </c>
@@ -18995,7 +18995,7 @@
         <v>223.04977715792859</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="23" t="s">
         <v>104</v>
       </c>
@@ -19019,7 +19019,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="23" t="s">
         <v>104</v>
       </c>
@@ -19037,7 +19037,7 @@
         <v>453.31516102290055</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="23" t="s">
         <v>110</v>
       </c>
@@ -19055,7 +19055,7 @@
         <v>448.34391098989863</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="23" t="s">
         <v>110</v>
       </c>
@@ -19076,7 +19076,7 @@
         <v>453.31516102290055</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="23" t="s">
         <v>120</v>
       </c>
@@ -19097,7 +19097,7 @@
         <v>448.34391098989863</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="23" t="s">
         <v>120</v>
       </c>
@@ -19124,7 +19124,7 @@
         <v>222.70190187345219</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="29"/>
@@ -19141,7 +19141,7 @@
         <v>448.34391098989863</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E42" s="24" t="s">
         <v>20</v>
       </c>
@@ -19153,22 +19153,22 @@
         <v>222.70190187345219</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L43">
         <f>SUM(L38:L42)</f>
         <v>1795.4067867496024</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B49" s="82" t="s">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B49" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="82"/>
-      <c r="D49" s="82"/>
-      <c r="E49" s="82"/>
-      <c r="F49" s="82"/>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C49" s="84"/>
+      <c r="D49" s="84"/>
+      <c r="E49" s="84"/>
+      <c r="F49" s="84"/>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="21" t="s">
         <v>22</v>
       </c>
@@ -19185,7 +19185,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="23" t="s">
         <v>177</v>
       </c>
@@ -19203,7 +19203,7 @@
         <v>672.33631795092469</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" s="23" t="s">
         <v>179</v>
       </c>
@@ -19230,7 +19230,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="23" t="s">
         <v>179</v>
       </c>
@@ -19257,7 +19257,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="23" t="s">
         <v>180</v>
       </c>
@@ -19284,7 +19284,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55" s="23" t="s">
         <v>182</v>
       </c>
@@ -19311,7 +19311,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56" s="23" t="s">
         <v>182</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" s="23" t="s">
         <v>185</v>
       </c>
@@ -19365,7 +19365,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58" s="23" t="s">
         <v>185</v>
       </c>
@@ -19392,7 +19392,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="E59" s="24" t="s">
         <v>20</v>
       </c>
@@ -19426,35 +19426,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="82" t="s">
+    <row r="2" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
       <c r="F3" s="22" t="s">
         <v>26</v>
       </c>
@@ -19462,7 +19462,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="44" t="s">
         <v>136</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>133</v>
       </c>
@@ -19502,7 +19502,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="23" t="s">
         <v>132</v>
       </c>
@@ -19523,7 +19523,7 @@
         <v>437.53920000000005</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="23" t="s">
         <v>130</v>
       </c>
@@ -19544,7 +19544,7 @@
         <v>437.53920000000005</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="23" t="s">
         <v>126</v>
       </c>
@@ -19565,7 +19565,7 @@
         <v>437.53920000000005</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E9" s="42"/>
       <c r="F9" s="47" t="s">
         <v>135</v>
@@ -19575,59 +19575,59 @@
         <v>1582.6176</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E10" s="42"/>
       <c r="F10" s="42"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E11" s="42"/>
       <c r="F11" s="42"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E13" s="42"/>
       <c r="F13" s="42"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E14" s="42"/>
       <c r="F14" s="42"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E15" s="42"/>
       <c r="F15" s="42"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E17" s="42"/>
       <c r="F17" s="42"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E18" s="42"/>
       <c r="F18" s="42"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E19" s="42"/>
       <c r="F19" s="42"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E20" s="42"/>
       <c r="F20" s="42"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E25" s="42"/>
       <c r="F25" s="42"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E26" s="42"/>
       <c r="F26" s="42"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E27" s="42"/>
       <c r="F27" s="42"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E28" s="42"/>
       <c r="F28" s="42"/>
     </row>
@@ -19647,31 +19647,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="82" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="84" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
       <c r="F3" s="22" t="s">
         <v>26</v>
       </c>
@@ -19679,7 +19679,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="44" t="s">
         <v>136</v>
       </c>
@@ -19699,7 +19699,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>133</v>
       </c>
@@ -19719,7 +19719,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="23" t="s">
         <v>132</v>
       </c>
@@ -19740,7 +19740,7 @@
         <v>293.26080000000002</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="23" t="s">
         <v>130</v>
       </c>
@@ -19761,7 +19761,7 @@
         <v>293.26080000000002</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="23" t="s">
         <v>126</v>
       </c>
@@ -19782,7 +19782,7 @@
         <v>293.26080000000002</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
@@ -19790,7 +19790,7 @@
       <c r="F9" s="46"/>
       <c r="G9" s="48"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E10" s="42"/>
       <c r="F10" s="47" t="s">
         <v>135</v>
@@ -19816,44 +19816,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="95" t="s">
+    <row r="2" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="89" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="82" t="s">
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="84" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
       <c r="F4" s="22" t="s">
         <v>26</v>
       </c>
@@ -19861,7 +19861,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="44" t="s">
         <v>136</v>
       </c>
@@ -19881,7 +19881,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="23" t="s">
         <v>133</v>
       </c>
@@ -19901,7 +19901,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="23" t="s">
         <v>132</v>
       </c>
@@ -19922,7 +19922,7 @@
         <v>401.92880000000002</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="23" t="s">
         <v>130</v>
       </c>
@@ -19943,7 +19943,7 @@
         <v>401.92880000000002</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E9" s="42"/>
       <c r="F9" s="47" t="s">
         <v>135</v>
@@ -19953,25 +19953,25 @@
         <v>1073.8576</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="87" t="s">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="90" t="s">
         <v>187</v>
       </c>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="88"/>
-      <c r="F12" s="89"/>
-    </row>
-    <row r="13" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="90" t="s">
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="92"/>
+    </row>
+    <row r="13" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="95" t="s">
         <v>138</v>
       </c>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="92"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="97"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="21" t="s">
         <v>22</v>
       </c>
@@ -19986,16 +19986,16 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="84">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="86">
         <v>2023</v>
       </c>
-      <c r="C15" s="85"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="86"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="88"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="44" t="s">
         <v>126</v>
       </c>
@@ -20013,16 +20013,16 @@
         <v>401.92880000000002</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="84">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="86">
         <v>2024</v>
       </c>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="86"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="88"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="23" t="s">
         <v>174</v>
       </c>
@@ -20040,7 +20040,7 @@
         <v>353.17520000000002</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="23" t="s">
         <v>17</v>
       </c>
@@ -20058,7 +20058,7 @@
         <v>365.17040000000003</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="23" t="s">
         <v>53</v>
       </c>
@@ -20076,7 +20076,7 @@
         <v>380.50320000000005</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="23" t="s">
         <v>72</v>
       </c>
@@ -20094,7 +20094,7 @@
         <v>380.50320000000005</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="23" t="s">
         <v>169</v>
       </c>
@@ -20111,7 +20111,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E23" s="47" t="s">
         <v>135</v>
       </c>
@@ -20121,25 +20121,25 @@
       </c>
       <c r="G23" s="27"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="87" t="s">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="90" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="89"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="90" t="s">
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="92"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="95" t="s">
         <v>138</v>
       </c>
-      <c r="C27" s="91"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="92"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C27" s="96"/>
+      <c r="D27" s="96"/>
+      <c r="E27" s="96"/>
+      <c r="F27" s="97"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="21" t="s">
         <v>22</v>
       </c>
@@ -20154,16 +20154,16 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="84">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="86">
         <v>2024</v>
       </c>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="86"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="88"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="23" t="s">
         <v>89</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="23" t="s">
         <v>90</v>
       </c>
@@ -20199,7 +20199,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="23" t="s">
         <v>91</v>
       </c>
@@ -20217,7 +20217,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="23" t="s">
         <v>92</v>
       </c>
@@ -20235,7 +20235,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="23" t="s">
         <v>104</v>
       </c>
@@ -20253,7 +20253,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="23" t="s">
         <v>110</v>
       </c>
@@ -20271,7 +20271,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="23" t="s">
         <v>120</v>
       </c>
@@ -20289,7 +20289,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="23" t="s">
         <v>177</v>
       </c>
@@ -20307,16 +20307,16 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="84">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="86">
         <v>2025</v>
       </c>
-      <c r="C38" s="85"/>
-      <c r="D38" s="85"/>
-      <c r="E38" s="85"/>
-      <c r="F38" s="86"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C38" s="87"/>
+      <c r="D38" s="87"/>
+      <c r="E38" s="87"/>
+      <c r="F38" s="88"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="23" t="s">
         <v>179</v>
       </c>
@@ -20334,7 +20334,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E40" s="47" t="s">
         <v>135</v>
       </c>
@@ -20343,7 +20343,7 @@
         <v>3337.4023200000001</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="50" t="s">
         <v>23</v>
       </c>
@@ -20352,7 +20352,7 @@
       <c r="E42" s="50"/>
       <c r="F42" s="50"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="21" t="s">
         <v>22</v>
       </c>
@@ -20369,7 +20369,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="23" t="s">
         <v>177</v>
       </c>
@@ -20387,7 +20387,7 @@
         <v>672.33631795092469</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="23" t="s">
         <v>179</v>
       </c>
@@ -20405,7 +20405,7 @@
         <v>448.34391098989863</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="23" t="s">
         <v>179</v>
       </c>
@@ -20423,7 +20423,7 @@
         <v>222.70190187345219</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="23" t="s">
         <v>180</v>
       </c>
@@ -20441,7 +20441,7 @@
         <v>672.33631795092469</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="23" t="s">
         <v>182</v>
       </c>
@@ -20459,7 +20459,7 @@
         <v>222.70190187345219</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="23" t="s">
         <v>182</v>
       </c>
@@ -20477,7 +20477,7 @@
         <v>448.34391098989863</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="23" t="s">
         <v>185</v>
       </c>
@@ -20495,7 +20495,7 @@
         <v>683.25904079431621</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="23" t="s">
         <v>185</v>
       </c>
@@ -20513,7 +20513,7 @@
         <v>683.25904079431621</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E52" s="24" t="s">
         <v>20</v>
       </c>
@@ -20522,7 +20522,7 @@
         <v>4053.2823432171836</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E56" t="s">
         <v>20</v>
       </c>
@@ -20533,6 +20533,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B29:F29"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B15:F15"/>
@@ -20541,11 +20546,6 @@
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="B29:F29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -20555,34 +20555,34 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="90" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="89"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="90" t="s">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="95" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="92"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="97"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>22</v>
       </c>
@@ -20597,16 +20597,16 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="84">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="86">
         <v>2024</v>
       </c>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="86"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="88"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
         <v>89</v>
       </c>
@@ -20624,7 +20624,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
         <v>90</v>
       </c>
@@ -20642,7 +20642,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>91</v>
       </c>
@@ -20660,7 +20660,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
         <v>92</v>
       </c>
@@ -20678,7 +20678,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>104</v>
       </c>
@@ -20696,7 +20696,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>110</v>
       </c>
@@ -20714,7 +20714,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>120</v>
       </c>
@@ -20732,7 +20732,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>177</v>
       </c>
@@ -20750,16 +20750,16 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="84">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="86">
         <v>2025</v>
       </c>
-      <c r="B13" s="85"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="86"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="88"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>179</v>
       </c>
@@ -20777,7 +20777,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>180</v>
       </c>
@@ -20795,7 +20795,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>198</v>
       </c>
@@ -20813,7 +20813,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>200</v>
       </c>
@@ -20831,7 +20831,7 @@
         <v>370.82248000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D18" s="47" t="s">
         <v>135</v>
       </c>
@@ -20840,25 +20840,25 @@
         <v>4449.8697599999996</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="87" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="90" t="s">
         <v>176</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="89"/>
-    </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="90" t="s">
+      <c r="B20" s="91"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="92"/>
+    </row>
+    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="95" t="s">
         <v>197</v>
       </c>
-      <c r="B21" s="91"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="92"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="96"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="97"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
         <v>22</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>177</v>
       </c>
@@ -20893,7 +20893,7 @@
         <v>672.33631795092469</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
         <v>179</v>
       </c>
@@ -20911,7 +20911,7 @@
         <v>448.34391098989863</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
         <v>179</v>
       </c>
@@ -20929,7 +20929,7 @@
         <v>222.70190187345219</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>180</v>
       </c>
@@ -20947,7 +20947,7 @@
         <v>672.33631795092469</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
         <v>182</v>
       </c>
@@ -20965,7 +20965,7 @@
         <v>222.70190187345219</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
         <v>182</v>
       </c>
@@ -20983,7 +20983,7 @@
         <v>448.34391098989863</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>185</v>
       </c>
@@ -21001,7 +21001,7 @@
         <v>683.25904079431621</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>185</v>
       </c>
@@ -21019,7 +21019,7 @@
         <v>683.25904079431621</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D31" s="24" t="s">
         <v>20</v>
       </c>
@@ -21028,25 +21028,25 @@
         <v>4053.2823432171836</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="87" t="s">
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="90" t="s">
         <v>176</v>
       </c>
-      <c r="B33" s="88"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="89"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="90" t="s">
+      <c r="B33" s="91"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="92"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="95" t="s">
         <v>137</v>
       </c>
-      <c r="B34" s="91"/>
-      <c r="C34" s="91"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="92"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="96"/>
+      <c r="C34" s="96"/>
+      <c r="D34" s="96"/>
+      <c r="E34" s="97"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
         <v>22</v>
       </c>
@@ -21061,16 +21061,16 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="84">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="86">
         <v>2025</v>
       </c>
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
-      <c r="D36" s="85"/>
-      <c r="E36" s="86"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="87"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="87"/>
+      <c r="E36" s="88"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
         <v>202</v>
       </c>
@@ -21088,7 +21088,7 @@
         <v>269.76208000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="s">
         <v>17</v>
       </c>
@@ -21106,7 +21106,7 @@
         <v>269.76208000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D39" s="47" t="s">
         <v>135</v>
       </c>
@@ -21115,19 +21115,19 @@
         <v>539.52416000000005</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D40" s="96"/>
-      <c r="E40" s="97"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D41" s="96"/>
-      <c r="E41" s="97"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D42" s="96"/>
-      <c r="E42" s="97"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D40" s="53"/>
+      <c r="E40" s="54"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D41" s="53"/>
+      <c r="E41" s="54"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D42" s="53"/>
+      <c r="E42" s="54"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D43" s="51" t="s">
         <v>20</v>
       </c>
@@ -21138,17 +21138,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A21:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
